--- a/sheets/rumman-calculator.xlsx
+++ b/sheets/rumman-calculator.xlsx
@@ -44091,9 +44091,12 @@
     <cfRule type="cellIs" priority="2" operator="equal" dxfId="6">
       <formula>"غير مكتمل"</formula>
     </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="8">
+      <formula>"محذوف"</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:L303">
-    <cfRule type="expression" priority="3" dxfId="2">
+    <cfRule type="expression" priority="4" dxfId="2">
       <formula>AND(MOD(ROW(),2)=1,$A4&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -44102,7 +44105,7 @@
       <formula1>"قطعة,رزمة,لفة,رول,كرتونة,كغ"</formula1>
     </dataValidation>
     <dataValidation sqref="I4:I303" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="قيمة غير صحيحة" error="اختر قيمة من القائمة." type="list">
-      <formula1>"مكتمل,غير مكتمل"</formula1>
+      <formula1>"مكتمل,غير مكتمل,محذوف"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/sheets/rumman-calculator.xlsx
+++ b/sheets/rumman-calculator.xlsx
@@ -20,9 +20,9 @@
     <sheet name="سجل التعديلات" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'البرادات'!$A$3:$W$303</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'البرادات'!$A$3:$X$303</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'البرادات'!$3:$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'المزارعون'!$A$3:$J$303</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'المزارعون'!$A$3:$K$303</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'المزارعون'!$3:$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'مشتريات الرمان'!$A$3:$Z$303</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'مشتريات الرمان'!$3:$3</definedName>
@@ -10280,7 +10280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W303"/>
+  <dimension ref="A1:X303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -10306,6 +10306,7 @@
     <col width="20" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
     <col hidden="1" width="12" customWidth="1" min="23" max="23"/>
+    <col hidden="1" width="15" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="44" customHeight="1">
@@ -10336,11 +10337,12 @@
       <c r="U1" s="32" t="n"/>
       <c r="V1" s="32" t="n"/>
       <c r="W1" s="32" t="n"/>
+      <c r="X1" s="32" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>بيانات كل براد وحالته. أعمدة «عند التقفيل» تُحفظ مرة واحدة لحظة التقفيل ولا تتغير بعدها.</t>
+          <t>بيانات كل براد وحالته. أعمدة «عند التقفيل» تُحفظ لحظة التقفيل ولا تغيّرها إعادة الفتح؛ إن أُعيد تقفيل البراد تُستبدل بأرقام التقفيل الأخير، والأرقام السابقة محفوظة في «سجل التعديلات».</t>
         </is>
       </c>
       <c r="B2" s="33" t="n"/>
@@ -10365,6 +10367,7 @@
       <c r="U2" s="33" t="n"/>
       <c r="V2" s="33" t="n"/>
       <c r="W2" s="33" t="n"/>
+      <c r="X2" s="33" t="n"/>
     </row>
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
@@ -10480,6 +10483,11 @@
       <c r="W3" s="35" t="inlineStr">
         <is>
           <t>الإصدار</t>
+        </is>
+      </c>
+      <c r="X3" s="34" t="inlineStr">
+        <is>
+          <t>مفتاح عدم التكرار</t>
         </is>
       </c>
     </row>
@@ -10567,6 +10575,7 @@
       <c r="W4" s="37" t="n">
         <v>1</v>
       </c>
+      <c r="X4" s="36" t="n"/>
     </row>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="36" t="inlineStr">
@@ -10628,6 +10637,7 @@
       <c r="W5" s="37" t="n">
         <v>1</v>
       </c>
+      <c r="X5" s="36" t="n"/>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="36" t="inlineStr">
@@ -10689,6 +10699,7 @@
       <c r="W6" s="37" t="n">
         <v>1</v>
       </c>
+      <c r="X6" s="36" t="n"/>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="36" t="n"/>
@@ -10714,6 +10725,7 @@
       <c r="U7" s="39" t="n"/>
       <c r="V7" s="38" t="n"/>
       <c r="W7" s="37" t="n"/>
+      <c r="X7" s="36" t="n"/>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="36" t="n"/>
@@ -10739,6 +10751,7 @@
       <c r="U8" s="39" t="n"/>
       <c r="V8" s="38" t="n"/>
       <c r="W8" s="37" t="n"/>
+      <c r="X8" s="36" t="n"/>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="36" t="n"/>
@@ -10764,6 +10777,7 @@
       <c r="U9" s="39" t="n"/>
       <c r="V9" s="38" t="n"/>
       <c r="W9" s="37" t="n"/>
+      <c r="X9" s="36" t="n"/>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="36" t="n"/>
@@ -10789,6 +10803,7 @@
       <c r="U10" s="39" t="n"/>
       <c r="V10" s="38" t="n"/>
       <c r="W10" s="37" t="n"/>
+      <c r="X10" s="36" t="n"/>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="36" t="n"/>
@@ -10814,6 +10829,7 @@
       <c r="U11" s="39" t="n"/>
       <c r="V11" s="38" t="n"/>
       <c r="W11" s="37" t="n"/>
+      <c r="X11" s="36" t="n"/>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="36" t="n"/>
@@ -10839,6 +10855,7 @@
       <c r="U12" s="39" t="n"/>
       <c r="V12" s="38" t="n"/>
       <c r="W12" s="37" t="n"/>
+      <c r="X12" s="36" t="n"/>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="36" t="n"/>
@@ -10864,6 +10881,7 @@
       <c r="U13" s="39" t="n"/>
       <c r="V13" s="38" t="n"/>
       <c r="W13" s="37" t="n"/>
+      <c r="X13" s="36" t="n"/>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="36" t="n"/>
@@ -10889,6 +10907,7 @@
       <c r="U14" s="39" t="n"/>
       <c r="V14" s="38" t="n"/>
       <c r="W14" s="37" t="n"/>
+      <c r="X14" s="36" t="n"/>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="36" t="n"/>
@@ -10914,6 +10933,7 @@
       <c r="U15" s="39" t="n"/>
       <c r="V15" s="38" t="n"/>
       <c r="W15" s="37" t="n"/>
+      <c r="X15" s="36" t="n"/>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="36" t="n"/>
@@ -10939,6 +10959,7 @@
       <c r="U16" s="39" t="n"/>
       <c r="V16" s="38" t="n"/>
       <c r="W16" s="37" t="n"/>
+      <c r="X16" s="36" t="n"/>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="36" t="n"/>
@@ -10964,6 +10985,7 @@
       <c r="U17" s="39" t="n"/>
       <c r="V17" s="38" t="n"/>
       <c r="W17" s="37" t="n"/>
+      <c r="X17" s="36" t="n"/>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="36" t="n"/>
@@ -10989,6 +11011,7 @@
       <c r="U18" s="39" t="n"/>
       <c r="V18" s="38" t="n"/>
       <c r="W18" s="37" t="n"/>
+      <c r="X18" s="36" t="n"/>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="36" t="n"/>
@@ -11014,6 +11037,7 @@
       <c r="U19" s="39" t="n"/>
       <c r="V19" s="38" t="n"/>
       <c r="W19" s="37" t="n"/>
+      <c r="X19" s="36" t="n"/>
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="36" t="n"/>
@@ -11039,6 +11063,7 @@
       <c r="U20" s="39" t="n"/>
       <c r="V20" s="38" t="n"/>
       <c r="W20" s="37" t="n"/>
+      <c r="X20" s="36" t="n"/>
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="36" t="n"/>
@@ -11064,6 +11089,7 @@
       <c r="U21" s="39" t="n"/>
       <c r="V21" s="38" t="n"/>
       <c r="W21" s="37" t="n"/>
+      <c r="X21" s="36" t="n"/>
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="36" t="n"/>
@@ -11089,6 +11115,7 @@
       <c r="U22" s="39" t="n"/>
       <c r="V22" s="38" t="n"/>
       <c r="W22" s="37" t="n"/>
+      <c r="X22" s="36" t="n"/>
     </row>
     <row r="23" ht="28" customHeight="1">
       <c r="A23" s="36" t="n"/>
@@ -11114,6 +11141,7 @@
       <c r="U23" s="39" t="n"/>
       <c r="V23" s="38" t="n"/>
       <c r="W23" s="37" t="n"/>
+      <c r="X23" s="36" t="n"/>
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="36" t="n"/>
@@ -11139,6 +11167,7 @@
       <c r="U24" s="39" t="n"/>
       <c r="V24" s="38" t="n"/>
       <c r="W24" s="37" t="n"/>
+      <c r="X24" s="36" t="n"/>
     </row>
     <row r="25" ht="28" customHeight="1">
       <c r="A25" s="36" t="n"/>
@@ -11164,6 +11193,7 @@
       <c r="U25" s="39" t="n"/>
       <c r="V25" s="38" t="n"/>
       <c r="W25" s="37" t="n"/>
+      <c r="X25" s="36" t="n"/>
     </row>
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="36" t="n"/>
@@ -11189,6 +11219,7 @@
       <c r="U26" s="39" t="n"/>
       <c r="V26" s="38" t="n"/>
       <c r="W26" s="37" t="n"/>
+      <c r="X26" s="36" t="n"/>
     </row>
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="36" t="n"/>
@@ -11214,6 +11245,7 @@
       <c r="U27" s="39" t="n"/>
       <c r="V27" s="38" t="n"/>
       <c r="W27" s="37" t="n"/>
+      <c r="X27" s="36" t="n"/>
     </row>
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="36" t="n"/>
@@ -11239,6 +11271,7 @@
       <c r="U28" s="39" t="n"/>
       <c r="V28" s="38" t="n"/>
       <c r="W28" s="37" t="n"/>
+      <c r="X28" s="36" t="n"/>
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="36" t="n"/>
@@ -11264,6 +11297,7 @@
       <c r="U29" s="39" t="n"/>
       <c r="V29" s="38" t="n"/>
       <c r="W29" s="37" t="n"/>
+      <c r="X29" s="36" t="n"/>
     </row>
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="36" t="n"/>
@@ -11289,6 +11323,7 @@
       <c r="U30" s="39" t="n"/>
       <c r="V30" s="38" t="n"/>
       <c r="W30" s="37" t="n"/>
+      <c r="X30" s="36" t="n"/>
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="36" t="n"/>
@@ -11314,6 +11349,7 @@
       <c r="U31" s="39" t="n"/>
       <c r="V31" s="38" t="n"/>
       <c r="W31" s="37" t="n"/>
+      <c r="X31" s="36" t="n"/>
     </row>
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="36" t="n"/>
@@ -11339,6 +11375,7 @@
       <c r="U32" s="39" t="n"/>
       <c r="V32" s="38" t="n"/>
       <c r="W32" s="37" t="n"/>
+      <c r="X32" s="36" t="n"/>
     </row>
     <row r="33" ht="28" customHeight="1">
       <c r="A33" s="36" t="n"/>
@@ -11364,6 +11401,7 @@
       <c r="U33" s="39" t="n"/>
       <c r="V33" s="38" t="n"/>
       <c r="W33" s="37" t="n"/>
+      <c r="X33" s="36" t="n"/>
     </row>
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="36" t="n"/>
@@ -11389,6 +11427,7 @@
       <c r="U34" s="39" t="n"/>
       <c r="V34" s="38" t="n"/>
       <c r="W34" s="37" t="n"/>
+      <c r="X34" s="36" t="n"/>
     </row>
     <row r="35" ht="28" customHeight="1">
       <c r="A35" s="36" t="n"/>
@@ -11414,6 +11453,7 @@
       <c r="U35" s="39" t="n"/>
       <c r="V35" s="38" t="n"/>
       <c r="W35" s="37" t="n"/>
+      <c r="X35" s="36" t="n"/>
     </row>
     <row r="36" ht="28" customHeight="1">
       <c r="A36" s="36" t="n"/>
@@ -11439,6 +11479,7 @@
       <c r="U36" s="39" t="n"/>
       <c r="V36" s="38" t="n"/>
       <c r="W36" s="37" t="n"/>
+      <c r="X36" s="36" t="n"/>
     </row>
     <row r="37" ht="28" customHeight="1">
       <c r="A37" s="36" t="n"/>
@@ -11464,6 +11505,7 @@
       <c r="U37" s="39" t="n"/>
       <c r="V37" s="38" t="n"/>
       <c r="W37" s="37" t="n"/>
+      <c r="X37" s="36" t="n"/>
     </row>
     <row r="38" ht="28" customHeight="1">
       <c r="A38" s="36" t="n"/>
@@ -11489,6 +11531,7 @@
       <c r="U38" s="39" t="n"/>
       <c r="V38" s="38" t="n"/>
       <c r="W38" s="37" t="n"/>
+      <c r="X38" s="36" t="n"/>
     </row>
     <row r="39" ht="28" customHeight="1">
       <c r="A39" s="36" t="n"/>
@@ -11514,6 +11557,7 @@
       <c r="U39" s="39" t="n"/>
       <c r="V39" s="38" t="n"/>
       <c r="W39" s="37" t="n"/>
+      <c r="X39" s="36" t="n"/>
     </row>
     <row r="40" ht="28" customHeight="1">
       <c r="A40" s="36" t="n"/>
@@ -11539,6 +11583,7 @@
       <c r="U40" s="39" t="n"/>
       <c r="V40" s="38" t="n"/>
       <c r="W40" s="37" t="n"/>
+      <c r="X40" s="36" t="n"/>
     </row>
     <row r="41" ht="28" customHeight="1">
       <c r="A41" s="36" t="n"/>
@@ -11564,6 +11609,7 @@
       <c r="U41" s="39" t="n"/>
       <c r="V41" s="38" t="n"/>
       <c r="W41" s="37" t="n"/>
+      <c r="X41" s="36" t="n"/>
     </row>
     <row r="42" ht="28" customHeight="1">
       <c r="A42" s="36" t="n"/>
@@ -11589,6 +11635,7 @@
       <c r="U42" s="39" t="n"/>
       <c r="V42" s="38" t="n"/>
       <c r="W42" s="37" t="n"/>
+      <c r="X42" s="36" t="n"/>
     </row>
     <row r="43" ht="28" customHeight="1">
       <c r="A43" s="36" t="n"/>
@@ -11614,6 +11661,7 @@
       <c r="U43" s="39" t="n"/>
       <c r="V43" s="38" t="n"/>
       <c r="W43" s="37" t="n"/>
+      <c r="X43" s="36" t="n"/>
     </row>
     <row r="44" ht="28" customHeight="1">
       <c r="A44" s="36" t="n"/>
@@ -11639,6 +11687,7 @@
       <c r="U44" s="39" t="n"/>
       <c r="V44" s="38" t="n"/>
       <c r="W44" s="37" t="n"/>
+      <c r="X44" s="36" t="n"/>
     </row>
     <row r="45" ht="28" customHeight="1">
       <c r="A45" s="36" t="n"/>
@@ -11664,6 +11713,7 @@
       <c r="U45" s="39" t="n"/>
       <c r="V45" s="38" t="n"/>
       <c r="W45" s="37" t="n"/>
+      <c r="X45" s="36" t="n"/>
     </row>
     <row r="46" ht="28" customHeight="1">
       <c r="A46" s="36" t="n"/>
@@ -11689,6 +11739,7 @@
       <c r="U46" s="39" t="n"/>
       <c r="V46" s="38" t="n"/>
       <c r="W46" s="37" t="n"/>
+      <c r="X46" s="36" t="n"/>
     </row>
     <row r="47" ht="28" customHeight="1">
       <c r="A47" s="36" t="n"/>
@@ -11714,6 +11765,7 @@
       <c r="U47" s="39" t="n"/>
       <c r="V47" s="38" t="n"/>
       <c r="W47" s="37" t="n"/>
+      <c r="X47" s="36" t="n"/>
     </row>
     <row r="48" ht="28" customHeight="1">
       <c r="A48" s="36" t="n"/>
@@ -11739,6 +11791,7 @@
       <c r="U48" s="39" t="n"/>
       <c r="V48" s="38" t="n"/>
       <c r="W48" s="37" t="n"/>
+      <c r="X48" s="36" t="n"/>
     </row>
     <row r="49" ht="28" customHeight="1">
       <c r="A49" s="36" t="n"/>
@@ -11764,6 +11817,7 @@
       <c r="U49" s="39" t="n"/>
       <c r="V49" s="38" t="n"/>
       <c r="W49" s="37" t="n"/>
+      <c r="X49" s="36" t="n"/>
     </row>
     <row r="50" ht="28" customHeight="1">
       <c r="A50" s="36" t="n"/>
@@ -11789,6 +11843,7 @@
       <c r="U50" s="39" t="n"/>
       <c r="V50" s="38" t="n"/>
       <c r="W50" s="37" t="n"/>
+      <c r="X50" s="36" t="n"/>
     </row>
     <row r="51" ht="28" customHeight="1">
       <c r="A51" s="36" t="n"/>
@@ -11814,6 +11869,7 @@
       <c r="U51" s="39" t="n"/>
       <c r="V51" s="38" t="n"/>
       <c r="W51" s="37" t="n"/>
+      <c r="X51" s="36" t="n"/>
     </row>
     <row r="52" ht="28" customHeight="1">
       <c r="A52" s="36" t="n"/>
@@ -11839,6 +11895,7 @@
       <c r="U52" s="39" t="n"/>
       <c r="V52" s="38" t="n"/>
       <c r="W52" s="37" t="n"/>
+      <c r="X52" s="36" t="n"/>
     </row>
     <row r="53" ht="28" customHeight="1">
       <c r="A53" s="36" t="n"/>
@@ -11864,6 +11921,7 @@
       <c r="U53" s="39" t="n"/>
       <c r="V53" s="38" t="n"/>
       <c r="W53" s="37" t="n"/>
+      <c r="X53" s="36" t="n"/>
     </row>
     <row r="54" ht="28" customHeight="1">
       <c r="A54" s="36" t="n"/>
@@ -11889,6 +11947,7 @@
       <c r="U54" s="39" t="n"/>
       <c r="V54" s="38" t="n"/>
       <c r="W54" s="37" t="n"/>
+      <c r="X54" s="36" t="n"/>
     </row>
     <row r="55" ht="28" customHeight="1">
       <c r="A55" s="36" t="n"/>
@@ -11914,6 +11973,7 @@
       <c r="U55" s="39" t="n"/>
       <c r="V55" s="38" t="n"/>
       <c r="W55" s="37" t="n"/>
+      <c r="X55" s="36" t="n"/>
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="36" t="n"/>
@@ -11939,6 +11999,7 @@
       <c r="U56" s="39" t="n"/>
       <c r="V56" s="38" t="n"/>
       <c r="W56" s="37" t="n"/>
+      <c r="X56" s="36" t="n"/>
     </row>
     <row r="57" ht="28" customHeight="1">
       <c r="A57" s="36" t="n"/>
@@ -11964,6 +12025,7 @@
       <c r="U57" s="39" t="n"/>
       <c r="V57" s="38" t="n"/>
       <c r="W57" s="37" t="n"/>
+      <c r="X57" s="36" t="n"/>
     </row>
     <row r="58" ht="28" customHeight="1">
       <c r="A58" s="36" t="n"/>
@@ -11989,6 +12051,7 @@
       <c r="U58" s="39" t="n"/>
       <c r="V58" s="38" t="n"/>
       <c r="W58" s="37" t="n"/>
+      <c r="X58" s="36" t="n"/>
     </row>
     <row r="59" ht="28" customHeight="1">
       <c r="A59" s="36" t="n"/>
@@ -12014,6 +12077,7 @@
       <c r="U59" s="39" t="n"/>
       <c r="V59" s="38" t="n"/>
       <c r="W59" s="37" t="n"/>
+      <c r="X59" s="36" t="n"/>
     </row>
     <row r="60" ht="28" customHeight="1">
       <c r="A60" s="36" t="n"/>
@@ -12039,6 +12103,7 @@
       <c r="U60" s="39" t="n"/>
       <c r="V60" s="38" t="n"/>
       <c r="W60" s="37" t="n"/>
+      <c r="X60" s="36" t="n"/>
     </row>
     <row r="61" ht="28" customHeight="1">
       <c r="A61" s="36" t="n"/>
@@ -12064,6 +12129,7 @@
       <c r="U61" s="39" t="n"/>
       <c r="V61" s="38" t="n"/>
       <c r="W61" s="37" t="n"/>
+      <c r="X61" s="36" t="n"/>
     </row>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="36" t="n"/>
@@ -12089,6 +12155,7 @@
       <c r="U62" s="39" t="n"/>
       <c r="V62" s="38" t="n"/>
       <c r="W62" s="37" t="n"/>
+      <c r="X62" s="36" t="n"/>
     </row>
     <row r="63" ht="28" customHeight="1">
       <c r="A63" s="36" t="n"/>
@@ -12114,6 +12181,7 @@
       <c r="U63" s="39" t="n"/>
       <c r="V63" s="38" t="n"/>
       <c r="W63" s="37" t="n"/>
+      <c r="X63" s="36" t="n"/>
     </row>
     <row r="64" ht="28" customHeight="1">
       <c r="A64" s="36" t="n"/>
@@ -12139,6 +12207,7 @@
       <c r="U64" s="39" t="n"/>
       <c r="V64" s="38" t="n"/>
       <c r="W64" s="37" t="n"/>
+      <c r="X64" s="36" t="n"/>
     </row>
     <row r="65" ht="28" customHeight="1">
       <c r="A65" s="36" t="n"/>
@@ -12164,6 +12233,7 @@
       <c r="U65" s="39" t="n"/>
       <c r="V65" s="38" t="n"/>
       <c r="W65" s="37" t="n"/>
+      <c r="X65" s="36" t="n"/>
     </row>
     <row r="66" ht="28" customHeight="1">
       <c r="A66" s="36" t="n"/>
@@ -12189,6 +12259,7 @@
       <c r="U66" s="39" t="n"/>
       <c r="V66" s="38" t="n"/>
       <c r="W66" s="37" t="n"/>
+      <c r="X66" s="36" t="n"/>
     </row>
     <row r="67" ht="28" customHeight="1">
       <c r="A67" s="36" t="n"/>
@@ -12214,6 +12285,7 @@
       <c r="U67" s="39" t="n"/>
       <c r="V67" s="38" t="n"/>
       <c r="W67" s="37" t="n"/>
+      <c r="X67" s="36" t="n"/>
     </row>
     <row r="68" ht="28" customHeight="1">
       <c r="A68" s="36" t="n"/>
@@ -12239,6 +12311,7 @@
       <c r="U68" s="39" t="n"/>
       <c r="V68" s="38" t="n"/>
       <c r="W68" s="37" t="n"/>
+      <c r="X68" s="36" t="n"/>
     </row>
     <row r="69" ht="28" customHeight="1">
       <c r="A69" s="36" t="n"/>
@@ -12264,6 +12337,7 @@
       <c r="U69" s="39" t="n"/>
       <c r="V69" s="38" t="n"/>
       <c r="W69" s="37" t="n"/>
+      <c r="X69" s="36" t="n"/>
     </row>
     <row r="70" ht="28" customHeight="1">
       <c r="A70" s="36" t="n"/>
@@ -12289,6 +12363,7 @@
       <c r="U70" s="39" t="n"/>
       <c r="V70" s="38" t="n"/>
       <c r="W70" s="37" t="n"/>
+      <c r="X70" s="36" t="n"/>
     </row>
     <row r="71" ht="28" customHeight="1">
       <c r="A71" s="36" t="n"/>
@@ -12314,6 +12389,7 @@
       <c r="U71" s="39" t="n"/>
       <c r="V71" s="38" t="n"/>
       <c r="W71" s="37" t="n"/>
+      <c r="X71" s="36" t="n"/>
     </row>
     <row r="72" ht="28" customHeight="1">
       <c r="A72" s="36" t="n"/>
@@ -12339,6 +12415,7 @@
       <c r="U72" s="39" t="n"/>
       <c r="V72" s="38" t="n"/>
       <c r="W72" s="37" t="n"/>
+      <c r="X72" s="36" t="n"/>
     </row>
     <row r="73" ht="28" customHeight="1">
       <c r="A73" s="36" t="n"/>
@@ -12364,6 +12441,7 @@
       <c r="U73" s="39" t="n"/>
       <c r="V73" s="38" t="n"/>
       <c r="W73" s="37" t="n"/>
+      <c r="X73" s="36" t="n"/>
     </row>
     <row r="74" ht="28" customHeight="1">
       <c r="A74" s="36" t="n"/>
@@ -12389,6 +12467,7 @@
       <c r="U74" s="39" t="n"/>
       <c r="V74" s="38" t="n"/>
       <c r="W74" s="37" t="n"/>
+      <c r="X74" s="36" t="n"/>
     </row>
     <row r="75" ht="28" customHeight="1">
       <c r="A75" s="36" t="n"/>
@@ -12414,6 +12493,7 @@
       <c r="U75" s="39" t="n"/>
       <c r="V75" s="38" t="n"/>
       <c r="W75" s="37" t="n"/>
+      <c r="X75" s="36" t="n"/>
     </row>
     <row r="76" ht="28" customHeight="1">
       <c r="A76" s="36" t="n"/>
@@ -12439,6 +12519,7 @@
       <c r="U76" s="39" t="n"/>
       <c r="V76" s="38" t="n"/>
       <c r="W76" s="37" t="n"/>
+      <c r="X76" s="36" t="n"/>
     </row>
     <row r="77" ht="28" customHeight="1">
       <c r="A77" s="36" t="n"/>
@@ -12464,6 +12545,7 @@
       <c r="U77" s="39" t="n"/>
       <c r="V77" s="38" t="n"/>
       <c r="W77" s="37" t="n"/>
+      <c r="X77" s="36" t="n"/>
     </row>
     <row r="78" ht="28" customHeight="1">
       <c r="A78" s="36" t="n"/>
@@ -12489,6 +12571,7 @@
       <c r="U78" s="39" t="n"/>
       <c r="V78" s="38" t="n"/>
       <c r="W78" s="37" t="n"/>
+      <c r="X78" s="36" t="n"/>
     </row>
     <row r="79" ht="28" customHeight="1">
       <c r="A79" s="36" t="n"/>
@@ -12514,6 +12597,7 @@
       <c r="U79" s="39" t="n"/>
       <c r="V79" s="38" t="n"/>
       <c r="W79" s="37" t="n"/>
+      <c r="X79" s="36" t="n"/>
     </row>
     <row r="80" ht="28" customHeight="1">
       <c r="A80" s="36" t="n"/>
@@ -12539,6 +12623,7 @@
       <c r="U80" s="39" t="n"/>
       <c r="V80" s="38" t="n"/>
       <c r="W80" s="37" t="n"/>
+      <c r="X80" s="36" t="n"/>
     </row>
     <row r="81" ht="28" customHeight="1">
       <c r="A81" s="36" t="n"/>
@@ -12564,6 +12649,7 @@
       <c r="U81" s="39" t="n"/>
       <c r="V81" s="38" t="n"/>
       <c r="W81" s="37" t="n"/>
+      <c r="X81" s="36" t="n"/>
     </row>
     <row r="82" ht="28" customHeight="1">
       <c r="A82" s="36" t="n"/>
@@ -12589,6 +12675,7 @@
       <c r="U82" s="39" t="n"/>
       <c r="V82" s="38" t="n"/>
       <c r="W82" s="37" t="n"/>
+      <c r="X82" s="36" t="n"/>
     </row>
     <row r="83" ht="28" customHeight="1">
       <c r="A83" s="36" t="n"/>
@@ -12614,6 +12701,7 @@
       <c r="U83" s="39" t="n"/>
       <c r="V83" s="38" t="n"/>
       <c r="W83" s="37" t="n"/>
+      <c r="X83" s="36" t="n"/>
     </row>
     <row r="84" ht="28" customHeight="1">
       <c r="A84" s="36" t="n"/>
@@ -12639,6 +12727,7 @@
       <c r="U84" s="39" t="n"/>
       <c r="V84" s="38" t="n"/>
       <c r="W84" s="37" t="n"/>
+      <c r="X84" s="36" t="n"/>
     </row>
     <row r="85" ht="28" customHeight="1">
       <c r="A85" s="36" t="n"/>
@@ -12664,6 +12753,7 @@
       <c r="U85" s="39" t="n"/>
       <c r="V85" s="38" t="n"/>
       <c r="W85" s="37" t="n"/>
+      <c r="X85" s="36" t="n"/>
     </row>
     <row r="86" ht="28" customHeight="1">
       <c r="A86" s="36" t="n"/>
@@ -12689,6 +12779,7 @@
       <c r="U86" s="39" t="n"/>
       <c r="V86" s="38" t="n"/>
       <c r="W86" s="37" t="n"/>
+      <c r="X86" s="36" t="n"/>
     </row>
     <row r="87" ht="28" customHeight="1">
       <c r="A87" s="36" t="n"/>
@@ -12714,6 +12805,7 @@
       <c r="U87" s="39" t="n"/>
       <c r="V87" s="38" t="n"/>
       <c r="W87" s="37" t="n"/>
+      <c r="X87" s="36" t="n"/>
     </row>
     <row r="88" ht="28" customHeight="1">
       <c r="A88" s="36" t="n"/>
@@ -12739,6 +12831,7 @@
       <c r="U88" s="39" t="n"/>
       <c r="V88" s="38" t="n"/>
       <c r="W88" s="37" t="n"/>
+      <c r="X88" s="36" t="n"/>
     </row>
     <row r="89" ht="28" customHeight="1">
       <c r="A89" s="36" t="n"/>
@@ -12764,6 +12857,7 @@
       <c r="U89" s="39" t="n"/>
       <c r="V89" s="38" t="n"/>
       <c r="W89" s="37" t="n"/>
+      <c r="X89" s="36" t="n"/>
     </row>
     <row r="90" ht="28" customHeight="1">
       <c r="A90" s="36" t="n"/>
@@ -12789,6 +12883,7 @@
       <c r="U90" s="39" t="n"/>
       <c r="V90" s="38" t="n"/>
       <c r="W90" s="37" t="n"/>
+      <c r="X90" s="36" t="n"/>
     </row>
     <row r="91" ht="28" customHeight="1">
       <c r="A91" s="36" t="n"/>
@@ -12814,6 +12909,7 @@
       <c r="U91" s="39" t="n"/>
       <c r="V91" s="38" t="n"/>
       <c r="W91" s="37" t="n"/>
+      <c r="X91" s="36" t="n"/>
     </row>
     <row r="92" ht="28" customHeight="1">
       <c r="A92" s="36" t="n"/>
@@ -12839,6 +12935,7 @@
       <c r="U92" s="39" t="n"/>
       <c r="V92" s="38" t="n"/>
       <c r="W92" s="37" t="n"/>
+      <c r="X92" s="36" t="n"/>
     </row>
     <row r="93" ht="28" customHeight="1">
       <c r="A93" s="36" t="n"/>
@@ -12864,6 +12961,7 @@
       <c r="U93" s="39" t="n"/>
       <c r="V93" s="38" t="n"/>
       <c r="W93" s="37" t="n"/>
+      <c r="X93" s="36" t="n"/>
     </row>
     <row r="94" ht="28" customHeight="1">
       <c r="A94" s="36" t="n"/>
@@ -12889,6 +12987,7 @@
       <c r="U94" s="39" t="n"/>
       <c r="V94" s="38" t="n"/>
       <c r="W94" s="37" t="n"/>
+      <c r="X94" s="36" t="n"/>
     </row>
     <row r="95" ht="28" customHeight="1">
       <c r="A95" s="36" t="n"/>
@@ -12914,6 +13013,7 @@
       <c r="U95" s="39" t="n"/>
       <c r="V95" s="38" t="n"/>
       <c r="W95" s="37" t="n"/>
+      <c r="X95" s="36" t="n"/>
     </row>
     <row r="96" ht="28" customHeight="1">
       <c r="A96" s="36" t="n"/>
@@ -12939,6 +13039,7 @@
       <c r="U96" s="39" t="n"/>
       <c r="V96" s="38" t="n"/>
       <c r="W96" s="37" t="n"/>
+      <c r="X96" s="36" t="n"/>
     </row>
     <row r="97" ht="28" customHeight="1">
       <c r="A97" s="36" t="n"/>
@@ -12964,6 +13065,7 @@
       <c r="U97" s="39" t="n"/>
       <c r="V97" s="38" t="n"/>
       <c r="W97" s="37" t="n"/>
+      <c r="X97" s="36" t="n"/>
     </row>
     <row r="98" ht="28" customHeight="1">
       <c r="A98" s="36" t="n"/>
@@ -12989,6 +13091,7 @@
       <c r="U98" s="39" t="n"/>
       <c r="V98" s="38" t="n"/>
       <c r="W98" s="37" t="n"/>
+      <c r="X98" s="36" t="n"/>
     </row>
     <row r="99" ht="28" customHeight="1">
       <c r="A99" s="36" t="n"/>
@@ -13014,6 +13117,7 @@
       <c r="U99" s="39" t="n"/>
       <c r="V99" s="38" t="n"/>
       <c r="W99" s="37" t="n"/>
+      <c r="X99" s="36" t="n"/>
     </row>
     <row r="100" ht="28" customHeight="1">
       <c r="A100" s="36" t="n"/>
@@ -13039,6 +13143,7 @@
       <c r="U100" s="39" t="n"/>
       <c r="V100" s="38" t="n"/>
       <c r="W100" s="37" t="n"/>
+      <c r="X100" s="36" t="n"/>
     </row>
     <row r="101" ht="28" customHeight="1">
       <c r="A101" s="36" t="n"/>
@@ -13064,6 +13169,7 @@
       <c r="U101" s="39" t="n"/>
       <c r="V101" s="38" t="n"/>
       <c r="W101" s="37" t="n"/>
+      <c r="X101" s="36" t="n"/>
     </row>
     <row r="102" ht="28" customHeight="1">
       <c r="A102" s="36" t="n"/>
@@ -13089,6 +13195,7 @@
       <c r="U102" s="39" t="n"/>
       <c r="V102" s="38" t="n"/>
       <c r="W102" s="37" t="n"/>
+      <c r="X102" s="36" t="n"/>
     </row>
     <row r="103" ht="28" customHeight="1">
       <c r="A103" s="36" t="n"/>
@@ -13114,6 +13221,7 @@
       <c r="U103" s="39" t="n"/>
       <c r="V103" s="38" t="n"/>
       <c r="W103" s="37" t="n"/>
+      <c r="X103" s="36" t="n"/>
     </row>
     <row r="104" ht="28" customHeight="1">
       <c r="A104" s="36" t="n"/>
@@ -13139,6 +13247,7 @@
       <c r="U104" s="39" t="n"/>
       <c r="V104" s="38" t="n"/>
       <c r="W104" s="37" t="n"/>
+      <c r="X104" s="36" t="n"/>
     </row>
     <row r="105" ht="28" customHeight="1">
       <c r="A105" s="36" t="n"/>
@@ -13164,6 +13273,7 @@
       <c r="U105" s="39" t="n"/>
       <c r="V105" s="38" t="n"/>
       <c r="W105" s="37" t="n"/>
+      <c r="X105" s="36" t="n"/>
     </row>
     <row r="106" ht="28" customHeight="1">
       <c r="A106" s="36" t="n"/>
@@ -13189,6 +13299,7 @@
       <c r="U106" s="39" t="n"/>
       <c r="V106" s="38" t="n"/>
       <c r="W106" s="37" t="n"/>
+      <c r="X106" s="36" t="n"/>
     </row>
     <row r="107" ht="28" customHeight="1">
       <c r="A107" s="36" t="n"/>
@@ -13214,6 +13325,7 @@
       <c r="U107" s="39" t="n"/>
       <c r="V107" s="38" t="n"/>
       <c r="W107" s="37" t="n"/>
+      <c r="X107" s="36" t="n"/>
     </row>
     <row r="108" ht="28" customHeight="1">
       <c r="A108" s="36" t="n"/>
@@ -13239,6 +13351,7 @@
       <c r="U108" s="39" t="n"/>
       <c r="V108" s="38" t="n"/>
       <c r="W108" s="37" t="n"/>
+      <c r="X108" s="36" t="n"/>
     </row>
     <row r="109" ht="28" customHeight="1">
       <c r="A109" s="36" t="n"/>
@@ -13264,6 +13377,7 @@
       <c r="U109" s="39" t="n"/>
       <c r="V109" s="38" t="n"/>
       <c r="W109" s="37" t="n"/>
+      <c r="X109" s="36" t="n"/>
     </row>
     <row r="110" ht="28" customHeight="1">
       <c r="A110" s="36" t="n"/>
@@ -13289,6 +13403,7 @@
       <c r="U110" s="39" t="n"/>
       <c r="V110" s="38" t="n"/>
       <c r="W110" s="37" t="n"/>
+      <c r="X110" s="36" t="n"/>
     </row>
     <row r="111" ht="28" customHeight="1">
       <c r="A111" s="36" t="n"/>
@@ -13314,6 +13429,7 @@
       <c r="U111" s="39" t="n"/>
       <c r="V111" s="38" t="n"/>
       <c r="W111" s="37" t="n"/>
+      <c r="X111" s="36" t="n"/>
     </row>
     <row r="112" ht="28" customHeight="1">
       <c r="A112" s="36" t="n"/>
@@ -13339,6 +13455,7 @@
       <c r="U112" s="39" t="n"/>
       <c r="V112" s="38" t="n"/>
       <c r="W112" s="37" t="n"/>
+      <c r="X112" s="36" t="n"/>
     </row>
     <row r="113" ht="28" customHeight="1">
       <c r="A113" s="36" t="n"/>
@@ -13364,6 +13481,7 @@
       <c r="U113" s="39" t="n"/>
       <c r="V113" s="38" t="n"/>
       <c r="W113" s="37" t="n"/>
+      <c r="X113" s="36" t="n"/>
     </row>
     <row r="114" ht="28" customHeight="1">
       <c r="A114" s="36" t="n"/>
@@ -13389,6 +13507,7 @@
       <c r="U114" s="39" t="n"/>
       <c r="V114" s="38" t="n"/>
       <c r="W114" s="37" t="n"/>
+      <c r="X114" s="36" t="n"/>
     </row>
     <row r="115" ht="28" customHeight="1">
       <c r="A115" s="36" t="n"/>
@@ -13414,6 +13533,7 @@
       <c r="U115" s="39" t="n"/>
       <c r="V115" s="38" t="n"/>
       <c r="W115" s="37" t="n"/>
+      <c r="X115" s="36" t="n"/>
     </row>
     <row r="116" ht="28" customHeight="1">
       <c r="A116" s="36" t="n"/>
@@ -13439,6 +13559,7 @@
       <c r="U116" s="39" t="n"/>
       <c r="V116" s="38" t="n"/>
       <c r="W116" s="37" t="n"/>
+      <c r="X116" s="36" t="n"/>
     </row>
     <row r="117" ht="28" customHeight="1">
       <c r="A117" s="36" t="n"/>
@@ -13464,6 +13585,7 @@
       <c r="U117" s="39" t="n"/>
       <c r="V117" s="38" t="n"/>
       <c r="W117" s="37" t="n"/>
+      <c r="X117" s="36" t="n"/>
     </row>
     <row r="118" ht="28" customHeight="1">
       <c r="A118" s="36" t="n"/>
@@ -13489,6 +13611,7 @@
       <c r="U118" s="39" t="n"/>
       <c r="V118" s="38" t="n"/>
       <c r="W118" s="37" t="n"/>
+      <c r="X118" s="36" t="n"/>
     </row>
     <row r="119" ht="28" customHeight="1">
       <c r="A119" s="36" t="n"/>
@@ -13514,6 +13637,7 @@
       <c r="U119" s="39" t="n"/>
       <c r="V119" s="38" t="n"/>
       <c r="W119" s="37" t="n"/>
+      <c r="X119" s="36" t="n"/>
     </row>
     <row r="120" ht="28" customHeight="1">
       <c r="A120" s="36" t="n"/>
@@ -13539,6 +13663,7 @@
       <c r="U120" s="39" t="n"/>
       <c r="V120" s="38" t="n"/>
       <c r="W120" s="37" t="n"/>
+      <c r="X120" s="36" t="n"/>
     </row>
     <row r="121" ht="28" customHeight="1">
       <c r="A121" s="36" t="n"/>
@@ -13564,6 +13689,7 @@
       <c r="U121" s="39" t="n"/>
       <c r="V121" s="38" t="n"/>
       <c r="W121" s="37" t="n"/>
+      <c r="X121" s="36" t="n"/>
     </row>
     <row r="122" ht="28" customHeight="1">
       <c r="A122" s="36" t="n"/>
@@ -13589,6 +13715,7 @@
       <c r="U122" s="39" t="n"/>
       <c r="V122" s="38" t="n"/>
       <c r="W122" s="37" t="n"/>
+      <c r="X122" s="36" t="n"/>
     </row>
     <row r="123" ht="28" customHeight="1">
       <c r="A123" s="36" t="n"/>
@@ -13614,6 +13741,7 @@
       <c r="U123" s="39" t="n"/>
       <c r="V123" s="38" t="n"/>
       <c r="W123" s="37" t="n"/>
+      <c r="X123" s="36" t="n"/>
     </row>
     <row r="124" ht="28" customHeight="1">
       <c r="A124" s="36" t="n"/>
@@ -13639,6 +13767,7 @@
       <c r="U124" s="39" t="n"/>
       <c r="V124" s="38" t="n"/>
       <c r="W124" s="37" t="n"/>
+      <c r="X124" s="36" t="n"/>
     </row>
     <row r="125" ht="28" customHeight="1">
       <c r="A125" s="36" t="n"/>
@@ -13664,6 +13793,7 @@
       <c r="U125" s="39" t="n"/>
       <c r="V125" s="38" t="n"/>
       <c r="W125" s="37" t="n"/>
+      <c r="X125" s="36" t="n"/>
     </row>
     <row r="126" ht="28" customHeight="1">
       <c r="A126" s="36" t="n"/>
@@ -13689,6 +13819,7 @@
       <c r="U126" s="39" t="n"/>
       <c r="V126" s="38" t="n"/>
       <c r="W126" s="37" t="n"/>
+      <c r="X126" s="36" t="n"/>
     </row>
     <row r="127" ht="28" customHeight="1">
       <c r="A127" s="36" t="n"/>
@@ -13714,6 +13845,7 @@
       <c r="U127" s="39" t="n"/>
       <c r="V127" s="38" t="n"/>
       <c r="W127" s="37" t="n"/>
+      <c r="X127" s="36" t="n"/>
     </row>
     <row r="128" ht="28" customHeight="1">
       <c r="A128" s="36" t="n"/>
@@ -13739,6 +13871,7 @@
       <c r="U128" s="39" t="n"/>
       <c r="V128" s="38" t="n"/>
       <c r="W128" s="37" t="n"/>
+      <c r="X128" s="36" t="n"/>
     </row>
     <row r="129" ht="28" customHeight="1">
       <c r="A129" s="36" t="n"/>
@@ -13764,6 +13897,7 @@
       <c r="U129" s="39" t="n"/>
       <c r="V129" s="38" t="n"/>
       <c r="W129" s="37" t="n"/>
+      <c r="X129" s="36" t="n"/>
     </row>
     <row r="130" ht="28" customHeight="1">
       <c r="A130" s="36" t="n"/>
@@ -13789,6 +13923,7 @@
       <c r="U130" s="39" t="n"/>
       <c r="V130" s="38" t="n"/>
       <c r="W130" s="37" t="n"/>
+      <c r="X130" s="36" t="n"/>
     </row>
     <row r="131" ht="28" customHeight="1">
       <c r="A131" s="36" t="n"/>
@@ -13814,6 +13949,7 @@
       <c r="U131" s="39" t="n"/>
       <c r="V131" s="38" t="n"/>
       <c r="W131" s="37" t="n"/>
+      <c r="X131" s="36" t="n"/>
     </row>
     <row r="132" ht="28" customHeight="1">
       <c r="A132" s="36" t="n"/>
@@ -13839,6 +13975,7 @@
       <c r="U132" s="39" t="n"/>
       <c r="V132" s="38" t="n"/>
       <c r="W132" s="37" t="n"/>
+      <c r="X132" s="36" t="n"/>
     </row>
     <row r="133" ht="28" customHeight="1">
       <c r="A133" s="36" t="n"/>
@@ -13864,6 +14001,7 @@
       <c r="U133" s="39" t="n"/>
       <c r="V133" s="38" t="n"/>
       <c r="W133" s="37" t="n"/>
+      <c r="X133" s="36" t="n"/>
     </row>
     <row r="134" ht="28" customHeight="1">
       <c r="A134" s="36" t="n"/>
@@ -13889,6 +14027,7 @@
       <c r="U134" s="39" t="n"/>
       <c r="V134" s="38" t="n"/>
       <c r="W134" s="37" t="n"/>
+      <c r="X134" s="36" t="n"/>
     </row>
     <row r="135" ht="28" customHeight="1">
       <c r="A135" s="36" t="n"/>
@@ -13914,6 +14053,7 @@
       <c r="U135" s="39" t="n"/>
       <c r="V135" s="38" t="n"/>
       <c r="W135" s="37" t="n"/>
+      <c r="X135" s="36" t="n"/>
     </row>
     <row r="136" ht="28" customHeight="1">
       <c r="A136" s="36" t="n"/>
@@ -13939,6 +14079,7 @@
       <c r="U136" s="39" t="n"/>
       <c r="V136" s="38" t="n"/>
       <c r="W136" s="37" t="n"/>
+      <c r="X136" s="36" t="n"/>
     </row>
     <row r="137" ht="28" customHeight="1">
       <c r="A137" s="36" t="n"/>
@@ -13964,6 +14105,7 @@
       <c r="U137" s="39" t="n"/>
       <c r="V137" s="38" t="n"/>
       <c r="W137" s="37" t="n"/>
+      <c r="X137" s="36" t="n"/>
     </row>
     <row r="138" ht="28" customHeight="1">
       <c r="A138" s="36" t="n"/>
@@ -13989,6 +14131,7 @@
       <c r="U138" s="39" t="n"/>
       <c r="V138" s="38" t="n"/>
       <c r="W138" s="37" t="n"/>
+      <c r="X138" s="36" t="n"/>
     </row>
     <row r="139" ht="28" customHeight="1">
       <c r="A139" s="36" t="n"/>
@@ -14014,6 +14157,7 @@
       <c r="U139" s="39" t="n"/>
       <c r="V139" s="38" t="n"/>
       <c r="W139" s="37" t="n"/>
+      <c r="X139" s="36" t="n"/>
     </row>
     <row r="140" ht="28" customHeight="1">
       <c r="A140" s="36" t="n"/>
@@ -14039,6 +14183,7 @@
       <c r="U140" s="39" t="n"/>
       <c r="V140" s="38" t="n"/>
       <c r="W140" s="37" t="n"/>
+      <c r="X140" s="36" t="n"/>
     </row>
     <row r="141" ht="28" customHeight="1">
       <c r="A141" s="36" t="n"/>
@@ -14064,6 +14209,7 @@
       <c r="U141" s="39" t="n"/>
       <c r="V141" s="38" t="n"/>
       <c r="W141" s="37" t="n"/>
+      <c r="X141" s="36" t="n"/>
     </row>
     <row r="142" ht="28" customHeight="1">
       <c r="A142" s="36" t="n"/>
@@ -14089,6 +14235,7 @@
       <c r="U142" s="39" t="n"/>
       <c r="V142" s="38" t="n"/>
       <c r="W142" s="37" t="n"/>
+      <c r="X142" s="36" t="n"/>
     </row>
     <row r="143" ht="28" customHeight="1">
       <c r="A143" s="36" t="n"/>
@@ -14114,6 +14261,7 @@
       <c r="U143" s="39" t="n"/>
       <c r="V143" s="38" t="n"/>
       <c r="W143" s="37" t="n"/>
+      <c r="X143" s="36" t="n"/>
     </row>
     <row r="144" ht="28" customHeight="1">
       <c r="A144" s="36" t="n"/>
@@ -14139,6 +14287,7 @@
       <c r="U144" s="39" t="n"/>
       <c r="V144" s="38" t="n"/>
       <c r="W144" s="37" t="n"/>
+      <c r="X144" s="36" t="n"/>
     </row>
     <row r="145" ht="28" customHeight="1">
       <c r="A145" s="36" t="n"/>
@@ -14164,6 +14313,7 @@
       <c r="U145" s="39" t="n"/>
       <c r="V145" s="38" t="n"/>
       <c r="W145" s="37" t="n"/>
+      <c r="X145" s="36" t="n"/>
     </row>
     <row r="146" ht="28" customHeight="1">
       <c r="A146" s="36" t="n"/>
@@ -14189,6 +14339,7 @@
       <c r="U146" s="39" t="n"/>
       <c r="V146" s="38" t="n"/>
       <c r="W146" s="37" t="n"/>
+      <c r="X146" s="36" t="n"/>
     </row>
     <row r="147" ht="28" customHeight="1">
       <c r="A147" s="36" t="n"/>
@@ -14214,6 +14365,7 @@
       <c r="U147" s="39" t="n"/>
       <c r="V147" s="38" t="n"/>
       <c r="W147" s="37" t="n"/>
+      <c r="X147" s="36" t="n"/>
     </row>
     <row r="148" ht="28" customHeight="1">
       <c r="A148" s="36" t="n"/>
@@ -14239,6 +14391,7 @@
       <c r="U148" s="39" t="n"/>
       <c r="V148" s="38" t="n"/>
       <c r="W148" s="37" t="n"/>
+      <c r="X148" s="36" t="n"/>
     </row>
     <row r="149" ht="28" customHeight="1">
       <c r="A149" s="36" t="n"/>
@@ -14264,6 +14417,7 @@
       <c r="U149" s="39" t="n"/>
       <c r="V149" s="38" t="n"/>
       <c r="W149" s="37" t="n"/>
+      <c r="X149" s="36" t="n"/>
     </row>
     <row r="150" ht="28" customHeight="1">
       <c r="A150" s="36" t="n"/>
@@ -14289,6 +14443,7 @@
       <c r="U150" s="39" t="n"/>
       <c r="V150" s="38" t="n"/>
       <c r="W150" s="37" t="n"/>
+      <c r="X150" s="36" t="n"/>
     </row>
     <row r="151" ht="28" customHeight="1">
       <c r="A151" s="36" t="n"/>
@@ -14314,6 +14469,7 @@
       <c r="U151" s="39" t="n"/>
       <c r="V151" s="38" t="n"/>
       <c r="W151" s="37" t="n"/>
+      <c r="X151" s="36" t="n"/>
     </row>
     <row r="152" ht="28" customHeight="1">
       <c r="A152" s="36" t="n"/>
@@ -14339,6 +14495,7 @@
       <c r="U152" s="39" t="n"/>
       <c r="V152" s="38" t="n"/>
       <c r="W152" s="37" t="n"/>
+      <c r="X152" s="36" t="n"/>
     </row>
     <row r="153" ht="28" customHeight="1">
       <c r="A153" s="36" t="n"/>
@@ -14364,6 +14521,7 @@
       <c r="U153" s="39" t="n"/>
       <c r="V153" s="38" t="n"/>
       <c r="W153" s="37" t="n"/>
+      <c r="X153" s="36" t="n"/>
     </row>
     <row r="154" ht="28" customHeight="1">
       <c r="A154" s="36" t="n"/>
@@ -14389,6 +14547,7 @@
       <c r="U154" s="39" t="n"/>
       <c r="V154" s="38" t="n"/>
       <c r="W154" s="37" t="n"/>
+      <c r="X154" s="36" t="n"/>
     </row>
     <row r="155" ht="28" customHeight="1">
       <c r="A155" s="36" t="n"/>
@@ -14414,6 +14573,7 @@
       <c r="U155" s="39" t="n"/>
       <c r="V155" s="38" t="n"/>
       <c r="W155" s="37" t="n"/>
+      <c r="X155" s="36" t="n"/>
     </row>
     <row r="156" ht="28" customHeight="1">
       <c r="A156" s="36" t="n"/>
@@ -14439,6 +14599,7 @@
       <c r="U156" s="39" t="n"/>
       <c r="V156" s="38" t="n"/>
       <c r="W156" s="37" t="n"/>
+      <c r="X156" s="36" t="n"/>
     </row>
     <row r="157" ht="28" customHeight="1">
       <c r="A157" s="36" t="n"/>
@@ -14464,6 +14625,7 @@
       <c r="U157" s="39" t="n"/>
       <c r="V157" s="38" t="n"/>
       <c r="W157" s="37" t="n"/>
+      <c r="X157" s="36" t="n"/>
     </row>
     <row r="158" ht="28" customHeight="1">
       <c r="A158" s="36" t="n"/>
@@ -14489,6 +14651,7 @@
       <c r="U158" s="39" t="n"/>
       <c r="V158" s="38" t="n"/>
       <c r="W158" s="37" t="n"/>
+      <c r="X158" s="36" t="n"/>
     </row>
     <row r="159" ht="28" customHeight="1">
       <c r="A159" s="36" t="n"/>
@@ -14514,6 +14677,7 @@
       <c r="U159" s="39" t="n"/>
       <c r="V159" s="38" t="n"/>
       <c r="W159" s="37" t="n"/>
+      <c r="X159" s="36" t="n"/>
     </row>
     <row r="160" ht="28" customHeight="1">
       <c r="A160" s="36" t="n"/>
@@ -14539,6 +14703,7 @@
       <c r="U160" s="39" t="n"/>
       <c r="V160" s="38" t="n"/>
       <c r="W160" s="37" t="n"/>
+      <c r="X160" s="36" t="n"/>
     </row>
     <row r="161" ht="28" customHeight="1">
       <c r="A161" s="36" t="n"/>
@@ -14564,6 +14729,7 @@
       <c r="U161" s="39" t="n"/>
       <c r="V161" s="38" t="n"/>
       <c r="W161" s="37" t="n"/>
+      <c r="X161" s="36" t="n"/>
     </row>
     <row r="162" ht="28" customHeight="1">
       <c r="A162" s="36" t="n"/>
@@ -14589,6 +14755,7 @@
       <c r="U162" s="39" t="n"/>
       <c r="V162" s="38" t="n"/>
       <c r="W162" s="37" t="n"/>
+      <c r="X162" s="36" t="n"/>
     </row>
     <row r="163" ht="28" customHeight="1">
       <c r="A163" s="36" t="n"/>
@@ -14614,6 +14781,7 @@
       <c r="U163" s="39" t="n"/>
       <c r="V163" s="38" t="n"/>
       <c r="W163" s="37" t="n"/>
+      <c r="X163" s="36" t="n"/>
     </row>
     <row r="164" ht="28" customHeight="1">
       <c r="A164" s="36" t="n"/>
@@ -14639,6 +14807,7 @@
       <c r="U164" s="39" t="n"/>
       <c r="V164" s="38" t="n"/>
       <c r="W164" s="37" t="n"/>
+      <c r="X164" s="36" t="n"/>
     </row>
     <row r="165" ht="28" customHeight="1">
       <c r="A165" s="36" t="n"/>
@@ -14664,6 +14833,7 @@
       <c r="U165" s="39" t="n"/>
       <c r="V165" s="38" t="n"/>
       <c r="W165" s="37" t="n"/>
+      <c r="X165" s="36" t="n"/>
     </row>
     <row r="166" ht="28" customHeight="1">
       <c r="A166" s="36" t="n"/>
@@ -14689,6 +14859,7 @@
       <c r="U166" s="39" t="n"/>
       <c r="V166" s="38" t="n"/>
       <c r="W166" s="37" t="n"/>
+      <c r="X166" s="36" t="n"/>
     </row>
     <row r="167" ht="28" customHeight="1">
       <c r="A167" s="36" t="n"/>
@@ -14714,6 +14885,7 @@
       <c r="U167" s="39" t="n"/>
       <c r="V167" s="38" t="n"/>
       <c r="W167" s="37" t="n"/>
+      <c r="X167" s="36" t="n"/>
     </row>
     <row r="168" ht="28" customHeight="1">
       <c r="A168" s="36" t="n"/>
@@ -14739,6 +14911,7 @@
       <c r="U168" s="39" t="n"/>
       <c r="V168" s="38" t="n"/>
       <c r="W168" s="37" t="n"/>
+      <c r="X168" s="36" t="n"/>
     </row>
     <row r="169" ht="28" customHeight="1">
       <c r="A169" s="36" t="n"/>
@@ -14764,6 +14937,7 @@
       <c r="U169" s="39" t="n"/>
       <c r="V169" s="38" t="n"/>
       <c r="W169" s="37" t="n"/>
+      <c r="X169" s="36" t="n"/>
     </row>
     <row r="170" ht="28" customHeight="1">
       <c r="A170" s="36" t="n"/>
@@ -14789,6 +14963,7 @@
       <c r="U170" s="39" t="n"/>
       <c r="V170" s="38" t="n"/>
       <c r="W170" s="37" t="n"/>
+      <c r="X170" s="36" t="n"/>
     </row>
     <row r="171" ht="28" customHeight="1">
       <c r="A171" s="36" t="n"/>
@@ -14814,6 +14989,7 @@
       <c r="U171" s="39" t="n"/>
       <c r="V171" s="38" t="n"/>
       <c r="W171" s="37" t="n"/>
+      <c r="X171" s="36" t="n"/>
     </row>
     <row r="172" ht="28" customHeight="1">
       <c r="A172" s="36" t="n"/>
@@ -14839,6 +15015,7 @@
       <c r="U172" s="39" t="n"/>
       <c r="V172" s="38" t="n"/>
       <c r="W172" s="37" t="n"/>
+      <c r="X172" s="36" t="n"/>
     </row>
     <row r="173" ht="28" customHeight="1">
       <c r="A173" s="36" t="n"/>
@@ -14864,6 +15041,7 @@
       <c r="U173" s="39" t="n"/>
       <c r="V173" s="38" t="n"/>
       <c r="W173" s="37" t="n"/>
+      <c r="X173" s="36" t="n"/>
     </row>
     <row r="174" ht="28" customHeight="1">
       <c r="A174" s="36" t="n"/>
@@ -14889,6 +15067,7 @@
       <c r="U174" s="39" t="n"/>
       <c r="V174" s="38" t="n"/>
       <c r="W174" s="37" t="n"/>
+      <c r="X174" s="36" t="n"/>
     </row>
     <row r="175" ht="28" customHeight="1">
       <c r="A175" s="36" t="n"/>
@@ -14914,6 +15093,7 @@
       <c r="U175" s="39" t="n"/>
       <c r="V175" s="38" t="n"/>
       <c r="W175" s="37" t="n"/>
+      <c r="X175" s="36" t="n"/>
     </row>
     <row r="176" ht="28" customHeight="1">
       <c r="A176" s="36" t="n"/>
@@ -14939,6 +15119,7 @@
       <c r="U176" s="39" t="n"/>
       <c r="V176" s="38" t="n"/>
       <c r="W176" s="37" t="n"/>
+      <c r="X176" s="36" t="n"/>
     </row>
     <row r="177" ht="28" customHeight="1">
       <c r="A177" s="36" t="n"/>
@@ -14964,6 +15145,7 @@
       <c r="U177" s="39" t="n"/>
       <c r="V177" s="38" t="n"/>
       <c r="W177" s="37" t="n"/>
+      <c r="X177" s="36" t="n"/>
     </row>
     <row r="178" ht="28" customHeight="1">
       <c r="A178" s="36" t="n"/>
@@ -14989,6 +15171,7 @@
       <c r="U178" s="39" t="n"/>
       <c r="V178" s="38" t="n"/>
       <c r="W178" s="37" t="n"/>
+      <c r="X178" s="36" t="n"/>
     </row>
     <row r="179" ht="28" customHeight="1">
       <c r="A179" s="36" t="n"/>
@@ -15014,6 +15197,7 @@
       <c r="U179" s="39" t="n"/>
       <c r="V179" s="38" t="n"/>
       <c r="W179" s="37" t="n"/>
+      <c r="X179" s="36" t="n"/>
     </row>
     <row r="180" ht="28" customHeight="1">
       <c r="A180" s="36" t="n"/>
@@ -15039,6 +15223,7 @@
       <c r="U180" s="39" t="n"/>
       <c r="V180" s="38" t="n"/>
       <c r="W180" s="37" t="n"/>
+      <c r="X180" s="36" t="n"/>
     </row>
     <row r="181" ht="28" customHeight="1">
       <c r="A181" s="36" t="n"/>
@@ -15064,6 +15249,7 @@
       <c r="U181" s="39" t="n"/>
       <c r="V181" s="38" t="n"/>
       <c r="W181" s="37" t="n"/>
+      <c r="X181" s="36" t="n"/>
     </row>
     <row r="182" ht="28" customHeight="1">
       <c r="A182" s="36" t="n"/>
@@ -15089,6 +15275,7 @@
       <c r="U182" s="39" t="n"/>
       <c r="V182" s="38" t="n"/>
       <c r="W182" s="37" t="n"/>
+      <c r="X182" s="36" t="n"/>
     </row>
     <row r="183" ht="28" customHeight="1">
       <c r="A183" s="36" t="n"/>
@@ -15114,6 +15301,7 @@
       <c r="U183" s="39" t="n"/>
       <c r="V183" s="38" t="n"/>
       <c r="W183" s="37" t="n"/>
+      <c r="X183" s="36" t="n"/>
     </row>
     <row r="184" ht="28" customHeight="1">
       <c r="A184" s="36" t="n"/>
@@ -15139,6 +15327,7 @@
       <c r="U184" s="39" t="n"/>
       <c r="V184" s="38" t="n"/>
       <c r="W184" s="37" t="n"/>
+      <c r="X184" s="36" t="n"/>
     </row>
     <row r="185" ht="28" customHeight="1">
       <c r="A185" s="36" t="n"/>
@@ -15164,6 +15353,7 @@
       <c r="U185" s="39" t="n"/>
       <c r="V185" s="38" t="n"/>
       <c r="W185" s="37" t="n"/>
+      <c r="X185" s="36" t="n"/>
     </row>
     <row r="186" ht="28" customHeight="1">
       <c r="A186" s="36" t="n"/>
@@ -15189,6 +15379,7 @@
       <c r="U186" s="39" t="n"/>
       <c r="V186" s="38" t="n"/>
       <c r="W186" s="37" t="n"/>
+      <c r="X186" s="36" t="n"/>
     </row>
     <row r="187" ht="28" customHeight="1">
       <c r="A187" s="36" t="n"/>
@@ -15214,6 +15405,7 @@
       <c r="U187" s="39" t="n"/>
       <c r="V187" s="38" t="n"/>
       <c r="W187" s="37" t="n"/>
+      <c r="X187" s="36" t="n"/>
     </row>
     <row r="188" ht="28" customHeight="1">
       <c r="A188" s="36" t="n"/>
@@ -15239,6 +15431,7 @@
       <c r="U188" s="39" t="n"/>
       <c r="V188" s="38" t="n"/>
       <c r="W188" s="37" t="n"/>
+      <c r="X188" s="36" t="n"/>
     </row>
     <row r="189" ht="28" customHeight="1">
       <c r="A189" s="36" t="n"/>
@@ -15264,6 +15457,7 @@
       <c r="U189" s="39" t="n"/>
       <c r="V189" s="38" t="n"/>
       <c r="W189" s="37" t="n"/>
+      <c r="X189" s="36" t="n"/>
     </row>
     <row r="190" ht="28" customHeight="1">
       <c r="A190" s="36" t="n"/>
@@ -15289,6 +15483,7 @@
       <c r="U190" s="39" t="n"/>
       <c r="V190" s="38" t="n"/>
       <c r="W190" s="37" t="n"/>
+      <c r="X190" s="36" t="n"/>
     </row>
     <row r="191" ht="28" customHeight="1">
       <c r="A191" s="36" t="n"/>
@@ -15314,6 +15509,7 @@
       <c r="U191" s="39" t="n"/>
       <c r="V191" s="38" t="n"/>
       <c r="W191" s="37" t="n"/>
+      <c r="X191" s="36" t="n"/>
     </row>
     <row r="192" ht="28" customHeight="1">
       <c r="A192" s="36" t="n"/>
@@ -15339,6 +15535,7 @@
       <c r="U192" s="39" t="n"/>
       <c r="V192" s="38" t="n"/>
       <c r="W192" s="37" t="n"/>
+      <c r="X192" s="36" t="n"/>
     </row>
     <row r="193" ht="28" customHeight="1">
       <c r="A193" s="36" t="n"/>
@@ -15364,6 +15561,7 @@
       <c r="U193" s="39" t="n"/>
       <c r="V193" s="38" t="n"/>
       <c r="W193" s="37" t="n"/>
+      <c r="X193" s="36" t="n"/>
     </row>
     <row r="194" ht="28" customHeight="1">
       <c r="A194" s="36" t="n"/>
@@ -15389,6 +15587,7 @@
       <c r="U194" s="39" t="n"/>
       <c r="V194" s="38" t="n"/>
       <c r="W194" s="37" t="n"/>
+      <c r="X194" s="36" t="n"/>
     </row>
     <row r="195" ht="28" customHeight="1">
       <c r="A195" s="36" t="n"/>
@@ -15414,6 +15613,7 @@
       <c r="U195" s="39" t="n"/>
       <c r="V195" s="38" t="n"/>
       <c r="W195" s="37" t="n"/>
+      <c r="X195" s="36" t="n"/>
     </row>
     <row r="196" ht="28" customHeight="1">
       <c r="A196" s="36" t="n"/>
@@ -15439,6 +15639,7 @@
       <c r="U196" s="39" t="n"/>
       <c r="V196" s="38" t="n"/>
       <c r="W196" s="37" t="n"/>
+      <c r="X196" s="36" t="n"/>
     </row>
     <row r="197" ht="28" customHeight="1">
       <c r="A197" s="36" t="n"/>
@@ -15464,6 +15665,7 @@
       <c r="U197" s="39" t="n"/>
       <c r="V197" s="38" t="n"/>
       <c r="W197" s="37" t="n"/>
+      <c r="X197" s="36" t="n"/>
     </row>
     <row r="198" ht="28" customHeight="1">
       <c r="A198" s="36" t="n"/>
@@ -15489,6 +15691,7 @@
       <c r="U198" s="39" t="n"/>
       <c r="V198" s="38" t="n"/>
       <c r="W198" s="37" t="n"/>
+      <c r="X198" s="36" t="n"/>
     </row>
     <row r="199" ht="28" customHeight="1">
       <c r="A199" s="36" t="n"/>
@@ -15514,6 +15717,7 @@
       <c r="U199" s="39" t="n"/>
       <c r="V199" s="38" t="n"/>
       <c r="W199" s="37" t="n"/>
+      <c r="X199" s="36" t="n"/>
     </row>
     <row r="200" ht="28" customHeight="1">
       <c r="A200" s="36" t="n"/>
@@ -15539,6 +15743,7 @@
       <c r="U200" s="39" t="n"/>
       <c r="V200" s="38" t="n"/>
       <c r="W200" s="37" t="n"/>
+      <c r="X200" s="36" t="n"/>
     </row>
     <row r="201" ht="28" customHeight="1">
       <c r="A201" s="36" t="n"/>
@@ -15564,6 +15769,7 @@
       <c r="U201" s="39" t="n"/>
       <c r="V201" s="38" t="n"/>
       <c r="W201" s="37" t="n"/>
+      <c r="X201" s="36" t="n"/>
     </row>
     <row r="202" ht="28" customHeight="1">
       <c r="A202" s="36" t="n"/>
@@ -15589,6 +15795,7 @@
       <c r="U202" s="39" t="n"/>
       <c r="V202" s="38" t="n"/>
       <c r="W202" s="37" t="n"/>
+      <c r="X202" s="36" t="n"/>
     </row>
     <row r="203" ht="28" customHeight="1">
       <c r="A203" s="36" t="n"/>
@@ -15614,6 +15821,7 @@
       <c r="U203" s="39" t="n"/>
       <c r="V203" s="38" t="n"/>
       <c r="W203" s="37" t="n"/>
+      <c r="X203" s="36" t="n"/>
     </row>
     <row r="204" ht="28" customHeight="1">
       <c r="A204" s="36" t="n"/>
@@ -15639,6 +15847,7 @@
       <c r="U204" s="39" t="n"/>
       <c r="V204" s="38" t="n"/>
       <c r="W204" s="37" t="n"/>
+      <c r="X204" s="36" t="n"/>
     </row>
     <row r="205" ht="28" customHeight="1">
       <c r="A205" s="36" t="n"/>
@@ -15664,6 +15873,7 @@
       <c r="U205" s="39" t="n"/>
       <c r="V205" s="38" t="n"/>
       <c r="W205" s="37" t="n"/>
+      <c r="X205" s="36" t="n"/>
     </row>
     <row r="206" ht="28" customHeight="1">
       <c r="A206" s="36" t="n"/>
@@ -15689,6 +15899,7 @@
       <c r="U206" s="39" t="n"/>
       <c r="V206" s="38" t="n"/>
       <c r="W206" s="37" t="n"/>
+      <c r="X206" s="36" t="n"/>
     </row>
     <row r="207" ht="28" customHeight="1">
       <c r="A207" s="36" t="n"/>
@@ -15714,6 +15925,7 @@
       <c r="U207" s="39" t="n"/>
       <c r="V207" s="38" t="n"/>
       <c r="W207" s="37" t="n"/>
+      <c r="X207" s="36" t="n"/>
     </row>
     <row r="208" ht="28" customHeight="1">
       <c r="A208" s="36" t="n"/>
@@ -15739,6 +15951,7 @@
       <c r="U208" s="39" t="n"/>
       <c r="V208" s="38" t="n"/>
       <c r="W208" s="37" t="n"/>
+      <c r="X208" s="36" t="n"/>
     </row>
     <row r="209" ht="28" customHeight="1">
       <c r="A209" s="36" t="n"/>
@@ -15764,6 +15977,7 @@
       <c r="U209" s="39" t="n"/>
       <c r="V209" s="38" t="n"/>
       <c r="W209" s="37" t="n"/>
+      <c r="X209" s="36" t="n"/>
     </row>
     <row r="210" ht="28" customHeight="1">
       <c r="A210" s="36" t="n"/>
@@ -15789,6 +16003,7 @@
       <c r="U210" s="39" t="n"/>
       <c r="V210" s="38" t="n"/>
       <c r="W210" s="37" t="n"/>
+      <c r="X210" s="36" t="n"/>
     </row>
     <row r="211" ht="28" customHeight="1">
       <c r="A211" s="36" t="n"/>
@@ -15814,6 +16029,7 @@
       <c r="U211" s="39" t="n"/>
       <c r="V211" s="38" t="n"/>
       <c r="W211" s="37" t="n"/>
+      <c r="X211" s="36" t="n"/>
     </row>
     <row r="212" ht="28" customHeight="1">
       <c r="A212" s="36" t="n"/>
@@ -15839,6 +16055,7 @@
       <c r="U212" s="39" t="n"/>
       <c r="V212" s="38" t="n"/>
       <c r="W212" s="37" t="n"/>
+      <c r="X212" s="36" t="n"/>
     </row>
     <row r="213" ht="28" customHeight="1">
       <c r="A213" s="36" t="n"/>
@@ -15864,6 +16081,7 @@
       <c r="U213" s="39" t="n"/>
       <c r="V213" s="38" t="n"/>
       <c r="W213" s="37" t="n"/>
+      <c r="X213" s="36" t="n"/>
     </row>
     <row r="214" ht="28" customHeight="1">
       <c r="A214" s="36" t="n"/>
@@ -15889,6 +16107,7 @@
       <c r="U214" s="39" t="n"/>
       <c r="V214" s="38" t="n"/>
       <c r="W214" s="37" t="n"/>
+      <c r="X214" s="36" t="n"/>
     </row>
     <row r="215" ht="28" customHeight="1">
       <c r="A215" s="36" t="n"/>
@@ -15914,6 +16133,7 @@
       <c r="U215" s="39" t="n"/>
       <c r="V215" s="38" t="n"/>
       <c r="W215" s="37" t="n"/>
+      <c r="X215" s="36" t="n"/>
     </row>
     <row r="216" ht="28" customHeight="1">
       <c r="A216" s="36" t="n"/>
@@ -15939,6 +16159,7 @@
       <c r="U216" s="39" t="n"/>
       <c r="V216" s="38" t="n"/>
       <c r="W216" s="37" t="n"/>
+      <c r="X216" s="36" t="n"/>
     </row>
     <row r="217" ht="28" customHeight="1">
       <c r="A217" s="36" t="n"/>
@@ -15964,6 +16185,7 @@
       <c r="U217" s="39" t="n"/>
       <c r="V217" s="38" t="n"/>
       <c r="W217" s="37" t="n"/>
+      <c r="X217" s="36" t="n"/>
     </row>
     <row r="218" ht="28" customHeight="1">
       <c r="A218" s="36" t="n"/>
@@ -15989,6 +16211,7 @@
       <c r="U218" s="39" t="n"/>
       <c r="V218" s="38" t="n"/>
       <c r="W218" s="37" t="n"/>
+      <c r="X218" s="36" t="n"/>
     </row>
     <row r="219" ht="28" customHeight="1">
       <c r="A219" s="36" t="n"/>
@@ -16014,6 +16237,7 @@
       <c r="U219" s="39" t="n"/>
       <c r="V219" s="38" t="n"/>
       <c r="W219" s="37" t="n"/>
+      <c r="X219" s="36" t="n"/>
     </row>
     <row r="220" ht="28" customHeight="1">
       <c r="A220" s="36" t="n"/>
@@ -16039,6 +16263,7 @@
       <c r="U220" s="39" t="n"/>
       <c r="V220" s="38" t="n"/>
       <c r="W220" s="37" t="n"/>
+      <c r="X220" s="36" t="n"/>
     </row>
     <row r="221" ht="28" customHeight="1">
       <c r="A221" s="36" t="n"/>
@@ -16064,6 +16289,7 @@
       <c r="U221" s="39" t="n"/>
       <c r="V221" s="38" t="n"/>
       <c r="W221" s="37" t="n"/>
+      <c r="X221" s="36" t="n"/>
     </row>
     <row r="222" ht="28" customHeight="1">
       <c r="A222" s="36" t="n"/>
@@ -16089,6 +16315,7 @@
       <c r="U222" s="39" t="n"/>
       <c r="V222" s="38" t="n"/>
       <c r="W222" s="37" t="n"/>
+      <c r="X222" s="36" t="n"/>
     </row>
     <row r="223" ht="28" customHeight="1">
       <c r="A223" s="36" t="n"/>
@@ -16114,6 +16341,7 @@
       <c r="U223" s="39" t="n"/>
       <c r="V223" s="38" t="n"/>
       <c r="W223" s="37" t="n"/>
+      <c r="X223" s="36" t="n"/>
     </row>
     <row r="224" ht="28" customHeight="1">
       <c r="A224" s="36" t="n"/>
@@ -16139,6 +16367,7 @@
       <c r="U224" s="39" t="n"/>
       <c r="V224" s="38" t="n"/>
       <c r="W224" s="37" t="n"/>
+      <c r="X224" s="36" t="n"/>
     </row>
     <row r="225" ht="28" customHeight="1">
       <c r="A225" s="36" t="n"/>
@@ -16164,6 +16393,7 @@
       <c r="U225" s="39" t="n"/>
       <c r="V225" s="38" t="n"/>
       <c r="W225" s="37" t="n"/>
+      <c r="X225" s="36" t="n"/>
     </row>
     <row r="226" ht="28" customHeight="1">
       <c r="A226" s="36" t="n"/>
@@ -16189,6 +16419,7 @@
       <c r="U226" s="39" t="n"/>
       <c r="V226" s="38" t="n"/>
       <c r="W226" s="37" t="n"/>
+      <c r="X226" s="36" t="n"/>
     </row>
     <row r="227" ht="28" customHeight="1">
       <c r="A227" s="36" t="n"/>
@@ -16214,6 +16445,7 @@
       <c r="U227" s="39" t="n"/>
       <c r="V227" s="38" t="n"/>
       <c r="W227" s="37" t="n"/>
+      <c r="X227" s="36" t="n"/>
     </row>
     <row r="228" ht="28" customHeight="1">
       <c r="A228" s="36" t="n"/>
@@ -16239,6 +16471,7 @@
       <c r="U228" s="39" t="n"/>
       <c r="V228" s="38" t="n"/>
       <c r="W228" s="37" t="n"/>
+      <c r="X228" s="36" t="n"/>
     </row>
     <row r="229" ht="28" customHeight="1">
       <c r="A229" s="36" t="n"/>
@@ -16264,6 +16497,7 @@
       <c r="U229" s="39" t="n"/>
       <c r="V229" s="38" t="n"/>
       <c r="W229" s="37" t="n"/>
+      <c r="X229" s="36" t="n"/>
     </row>
     <row r="230" ht="28" customHeight="1">
       <c r="A230" s="36" t="n"/>
@@ -16289,6 +16523,7 @@
       <c r="U230" s="39" t="n"/>
       <c r="V230" s="38" t="n"/>
       <c r="W230" s="37" t="n"/>
+      <c r="X230" s="36" t="n"/>
     </row>
     <row r="231" ht="28" customHeight="1">
       <c r="A231" s="36" t="n"/>
@@ -16314,6 +16549,7 @@
       <c r="U231" s="39" t="n"/>
       <c r="V231" s="38" t="n"/>
       <c r="W231" s="37" t="n"/>
+      <c r="X231" s="36" t="n"/>
     </row>
     <row r="232" ht="28" customHeight="1">
       <c r="A232" s="36" t="n"/>
@@ -16339,6 +16575,7 @@
       <c r="U232" s="39" t="n"/>
       <c r="V232" s="38" t="n"/>
       <c r="W232" s="37" t="n"/>
+      <c r="X232" s="36" t="n"/>
     </row>
     <row r="233" ht="28" customHeight="1">
       <c r="A233" s="36" t="n"/>
@@ -16364,6 +16601,7 @@
       <c r="U233" s="39" t="n"/>
       <c r="V233" s="38" t="n"/>
       <c r="W233" s="37" t="n"/>
+      <c r="X233" s="36" t="n"/>
     </row>
     <row r="234" ht="28" customHeight="1">
       <c r="A234" s="36" t="n"/>
@@ -16389,6 +16627,7 @@
       <c r="U234" s="39" t="n"/>
       <c r="V234" s="38" t="n"/>
       <c r="W234" s="37" t="n"/>
+      <c r="X234" s="36" t="n"/>
     </row>
     <row r="235" ht="28" customHeight="1">
       <c r="A235" s="36" t="n"/>
@@ -16414,6 +16653,7 @@
       <c r="U235" s="39" t="n"/>
       <c r="V235" s="38" t="n"/>
       <c r="W235" s="37" t="n"/>
+      <c r="X235" s="36" t="n"/>
     </row>
     <row r="236" ht="28" customHeight="1">
       <c r="A236" s="36" t="n"/>
@@ -16439,6 +16679,7 @@
       <c r="U236" s="39" t="n"/>
       <c r="V236" s="38" t="n"/>
       <c r="W236" s="37" t="n"/>
+      <c r="X236" s="36" t="n"/>
     </row>
     <row r="237" ht="28" customHeight="1">
       <c r="A237" s="36" t="n"/>
@@ -16464,6 +16705,7 @@
       <c r="U237" s="39" t="n"/>
       <c r="V237" s="38" t="n"/>
       <c r="W237" s="37" t="n"/>
+      <c r="X237" s="36" t="n"/>
     </row>
     <row r="238" ht="28" customHeight="1">
       <c r="A238" s="36" t="n"/>
@@ -16489,6 +16731,7 @@
       <c r="U238" s="39" t="n"/>
       <c r="V238" s="38" t="n"/>
       <c r="W238" s="37" t="n"/>
+      <c r="X238" s="36" t="n"/>
     </row>
     <row r="239" ht="28" customHeight="1">
       <c r="A239" s="36" t="n"/>
@@ -16514,6 +16757,7 @@
       <c r="U239" s="39" t="n"/>
       <c r="V239" s="38" t="n"/>
       <c r="W239" s="37" t="n"/>
+      <c r="X239" s="36" t="n"/>
     </row>
     <row r="240" ht="28" customHeight="1">
       <c r="A240" s="36" t="n"/>
@@ -16539,6 +16783,7 @@
       <c r="U240" s="39" t="n"/>
       <c r="V240" s="38" t="n"/>
       <c r="W240" s="37" t="n"/>
+      <c r="X240" s="36" t="n"/>
     </row>
     <row r="241" ht="28" customHeight="1">
       <c r="A241" s="36" t="n"/>
@@ -16564,6 +16809,7 @@
       <c r="U241" s="39" t="n"/>
       <c r="V241" s="38" t="n"/>
       <c r="W241" s="37" t="n"/>
+      <c r="X241" s="36" t="n"/>
     </row>
     <row r="242" ht="28" customHeight="1">
       <c r="A242" s="36" t="n"/>
@@ -16589,6 +16835,7 @@
       <c r="U242" s="39" t="n"/>
       <c r="V242" s="38" t="n"/>
       <c r="W242" s="37" t="n"/>
+      <c r="X242" s="36" t="n"/>
     </row>
     <row r="243" ht="28" customHeight="1">
       <c r="A243" s="36" t="n"/>
@@ -16614,6 +16861,7 @@
       <c r="U243" s="39" t="n"/>
       <c r="V243" s="38" t="n"/>
       <c r="W243" s="37" t="n"/>
+      <c r="X243" s="36" t="n"/>
     </row>
     <row r="244" ht="28" customHeight="1">
       <c r="A244" s="36" t="n"/>
@@ -16639,6 +16887,7 @@
       <c r="U244" s="39" t="n"/>
       <c r="V244" s="38" t="n"/>
       <c r="W244" s="37" t="n"/>
+      <c r="X244" s="36" t="n"/>
     </row>
     <row r="245" ht="28" customHeight="1">
       <c r="A245" s="36" t="n"/>
@@ -16664,6 +16913,7 @@
       <c r="U245" s="39" t="n"/>
       <c r="V245" s="38" t="n"/>
       <c r="W245" s="37" t="n"/>
+      <c r="X245" s="36" t="n"/>
     </row>
     <row r="246" ht="28" customHeight="1">
       <c r="A246" s="36" t="n"/>
@@ -16689,6 +16939,7 @@
       <c r="U246" s="39" t="n"/>
       <c r="V246" s="38" t="n"/>
       <c r="W246" s="37" t="n"/>
+      <c r="X246" s="36" t="n"/>
     </row>
     <row r="247" ht="28" customHeight="1">
       <c r="A247" s="36" t="n"/>
@@ -16714,6 +16965,7 @@
       <c r="U247" s="39" t="n"/>
       <c r="V247" s="38" t="n"/>
       <c r="W247" s="37" t="n"/>
+      <c r="X247" s="36" t="n"/>
     </row>
     <row r="248" ht="28" customHeight="1">
       <c r="A248" s="36" t="n"/>
@@ -16739,6 +16991,7 @@
       <c r="U248" s="39" t="n"/>
       <c r="V248" s="38" t="n"/>
       <c r="W248" s="37" t="n"/>
+      <c r="X248" s="36" t="n"/>
     </row>
     <row r="249" ht="28" customHeight="1">
       <c r="A249" s="36" t="n"/>
@@ -16764,6 +17017,7 @@
       <c r="U249" s="39" t="n"/>
       <c r="V249" s="38" t="n"/>
       <c r="W249" s="37" t="n"/>
+      <c r="X249" s="36" t="n"/>
     </row>
     <row r="250" ht="28" customHeight="1">
       <c r="A250" s="36" t="n"/>
@@ -16789,6 +17043,7 @@
       <c r="U250" s="39" t="n"/>
       <c r="V250" s="38" t="n"/>
       <c r="W250" s="37" t="n"/>
+      <c r="X250" s="36" t="n"/>
     </row>
     <row r="251" ht="28" customHeight="1">
       <c r="A251" s="36" t="n"/>
@@ -16814,6 +17069,7 @@
       <c r="U251" s="39" t="n"/>
       <c r="V251" s="38" t="n"/>
       <c r="W251" s="37" t="n"/>
+      <c r="X251" s="36" t="n"/>
     </row>
     <row r="252" ht="28" customHeight="1">
       <c r="A252" s="36" t="n"/>
@@ -16839,6 +17095,7 @@
       <c r="U252" s="39" t="n"/>
       <c r="V252" s="38" t="n"/>
       <c r="W252" s="37" t="n"/>
+      <c r="X252" s="36" t="n"/>
     </row>
     <row r="253" ht="28" customHeight="1">
       <c r="A253" s="36" t="n"/>
@@ -16864,6 +17121,7 @@
       <c r="U253" s="39" t="n"/>
       <c r="V253" s="38" t="n"/>
       <c r="W253" s="37" t="n"/>
+      <c r="X253" s="36" t="n"/>
     </row>
     <row r="254" ht="28" customHeight="1">
       <c r="A254" s="36" t="n"/>
@@ -16889,6 +17147,7 @@
       <c r="U254" s="39" t="n"/>
       <c r="V254" s="38" t="n"/>
       <c r="W254" s="37" t="n"/>
+      <c r="X254" s="36" t="n"/>
     </row>
     <row r="255" ht="28" customHeight="1">
       <c r="A255" s="36" t="n"/>
@@ -16914,6 +17173,7 @@
       <c r="U255" s="39" t="n"/>
       <c r="V255" s="38" t="n"/>
       <c r="W255" s="37" t="n"/>
+      <c r="X255" s="36" t="n"/>
     </row>
     <row r="256" ht="28" customHeight="1">
       <c r="A256" s="36" t="n"/>
@@ -16939,6 +17199,7 @@
       <c r="U256" s="39" t="n"/>
       <c r="V256" s="38" t="n"/>
       <c r="W256" s="37" t="n"/>
+      <c r="X256" s="36" t="n"/>
     </row>
     <row r="257" ht="28" customHeight="1">
       <c r="A257" s="36" t="n"/>
@@ -16964,6 +17225,7 @@
       <c r="U257" s="39" t="n"/>
       <c r="V257" s="38" t="n"/>
       <c r="W257" s="37" t="n"/>
+      <c r="X257" s="36" t="n"/>
     </row>
     <row r="258" ht="28" customHeight="1">
       <c r="A258" s="36" t="n"/>
@@ -16989,6 +17251,7 @@
       <c r="U258" s="39" t="n"/>
       <c r="V258" s="38" t="n"/>
       <c r="W258" s="37" t="n"/>
+      <c r="X258" s="36" t="n"/>
     </row>
     <row r="259" ht="28" customHeight="1">
       <c r="A259" s="36" t="n"/>
@@ -17014,6 +17277,7 @@
       <c r="U259" s="39" t="n"/>
       <c r="V259" s="38" t="n"/>
       <c r="W259" s="37" t="n"/>
+      <c r="X259" s="36" t="n"/>
     </row>
     <row r="260" ht="28" customHeight="1">
       <c r="A260" s="36" t="n"/>
@@ -17039,6 +17303,7 @@
       <c r="U260" s="39" t="n"/>
       <c r="V260" s="38" t="n"/>
       <c r="W260" s="37" t="n"/>
+      <c r="X260" s="36" t="n"/>
     </row>
     <row r="261" ht="28" customHeight="1">
       <c r="A261" s="36" t="n"/>
@@ -17064,6 +17329,7 @@
       <c r="U261" s="39" t="n"/>
       <c r="V261" s="38" t="n"/>
       <c r="W261" s="37" t="n"/>
+      <c r="X261" s="36" t="n"/>
     </row>
     <row r="262" ht="28" customHeight="1">
       <c r="A262" s="36" t="n"/>
@@ -17089,6 +17355,7 @@
       <c r="U262" s="39" t="n"/>
       <c r="V262" s="38" t="n"/>
       <c r="W262" s="37" t="n"/>
+      <c r="X262" s="36" t="n"/>
     </row>
     <row r="263" ht="28" customHeight="1">
       <c r="A263" s="36" t="n"/>
@@ -17114,6 +17381,7 @@
       <c r="U263" s="39" t="n"/>
       <c r="V263" s="38" t="n"/>
       <c r="W263" s="37" t="n"/>
+      <c r="X263" s="36" t="n"/>
     </row>
     <row r="264" ht="28" customHeight="1">
       <c r="A264" s="36" t="n"/>
@@ -17139,6 +17407,7 @@
       <c r="U264" s="39" t="n"/>
       <c r="V264" s="38" t="n"/>
       <c r="W264" s="37" t="n"/>
+      <c r="X264" s="36" t="n"/>
     </row>
     <row r="265" ht="28" customHeight="1">
       <c r="A265" s="36" t="n"/>
@@ -17164,6 +17433,7 @@
       <c r="U265" s="39" t="n"/>
       <c r="V265" s="38" t="n"/>
       <c r="W265" s="37" t="n"/>
+      <c r="X265" s="36" t="n"/>
     </row>
     <row r="266" ht="28" customHeight="1">
       <c r="A266" s="36" t="n"/>
@@ -17189,6 +17459,7 @@
       <c r="U266" s="39" t="n"/>
       <c r="V266" s="38" t="n"/>
       <c r="W266" s="37" t="n"/>
+      <c r="X266" s="36" t="n"/>
     </row>
     <row r="267" ht="28" customHeight="1">
       <c r="A267" s="36" t="n"/>
@@ -17214,6 +17485,7 @@
       <c r="U267" s="39" t="n"/>
       <c r="V267" s="38" t="n"/>
       <c r="W267" s="37" t="n"/>
+      <c r="X267" s="36" t="n"/>
     </row>
     <row r="268" ht="28" customHeight="1">
       <c r="A268" s="36" t="n"/>
@@ -17239,6 +17511,7 @@
       <c r="U268" s="39" t="n"/>
       <c r="V268" s="38" t="n"/>
       <c r="W268" s="37" t="n"/>
+      <c r="X268" s="36" t="n"/>
     </row>
     <row r="269" ht="28" customHeight="1">
       <c r="A269" s="36" t="n"/>
@@ -17264,6 +17537,7 @@
       <c r="U269" s="39" t="n"/>
       <c r="V269" s="38" t="n"/>
       <c r="W269" s="37" t="n"/>
+      <c r="X269" s="36" t="n"/>
     </row>
     <row r="270" ht="28" customHeight="1">
       <c r="A270" s="36" t="n"/>
@@ -17289,6 +17563,7 @@
       <c r="U270" s="39" t="n"/>
       <c r="V270" s="38" t="n"/>
       <c r="W270" s="37" t="n"/>
+      <c r="X270" s="36" t="n"/>
     </row>
     <row r="271" ht="28" customHeight="1">
       <c r="A271" s="36" t="n"/>
@@ -17314,6 +17589,7 @@
       <c r="U271" s="39" t="n"/>
       <c r="V271" s="38" t="n"/>
       <c r="W271" s="37" t="n"/>
+      <c r="X271" s="36" t="n"/>
     </row>
     <row r="272" ht="28" customHeight="1">
       <c r="A272" s="36" t="n"/>
@@ -17339,6 +17615,7 @@
       <c r="U272" s="39" t="n"/>
       <c r="V272" s="38" t="n"/>
       <c r="W272" s="37" t="n"/>
+      <c r="X272" s="36" t="n"/>
     </row>
     <row r="273" ht="28" customHeight="1">
       <c r="A273" s="36" t="n"/>
@@ -17364,6 +17641,7 @@
       <c r="U273" s="39" t="n"/>
       <c r="V273" s="38" t="n"/>
       <c r="W273" s="37" t="n"/>
+      <c r="X273" s="36" t="n"/>
     </row>
     <row r="274" ht="28" customHeight="1">
       <c r="A274" s="36" t="n"/>
@@ -17389,6 +17667,7 @@
       <c r="U274" s="39" t="n"/>
       <c r="V274" s="38" t="n"/>
       <c r="W274" s="37" t="n"/>
+      <c r="X274" s="36" t="n"/>
     </row>
     <row r="275" ht="28" customHeight="1">
       <c r="A275" s="36" t="n"/>
@@ -17414,6 +17693,7 @@
       <c r="U275" s="39" t="n"/>
       <c r="V275" s="38" t="n"/>
       <c r="W275" s="37" t="n"/>
+      <c r="X275" s="36" t="n"/>
     </row>
     <row r="276" ht="28" customHeight="1">
       <c r="A276" s="36" t="n"/>
@@ -17439,6 +17719,7 @@
       <c r="U276" s="39" t="n"/>
       <c r="V276" s="38" t="n"/>
       <c r="W276" s="37" t="n"/>
+      <c r="X276" s="36" t="n"/>
     </row>
     <row r="277" ht="28" customHeight="1">
       <c r="A277" s="36" t="n"/>
@@ -17464,6 +17745,7 @@
       <c r="U277" s="39" t="n"/>
       <c r="V277" s="38" t="n"/>
       <c r="W277" s="37" t="n"/>
+      <c r="X277" s="36" t="n"/>
     </row>
     <row r="278" ht="28" customHeight="1">
       <c r="A278" s="36" t="n"/>
@@ -17489,6 +17771,7 @@
       <c r="U278" s="39" t="n"/>
       <c r="V278" s="38" t="n"/>
       <c r="W278" s="37" t="n"/>
+      <c r="X278" s="36" t="n"/>
     </row>
     <row r="279" ht="28" customHeight="1">
       <c r="A279" s="36" t="n"/>
@@ -17514,6 +17797,7 @@
       <c r="U279" s="39" t="n"/>
       <c r="V279" s="38" t="n"/>
       <c r="W279" s="37" t="n"/>
+      <c r="X279" s="36" t="n"/>
     </row>
     <row r="280" ht="28" customHeight="1">
       <c r="A280" s="36" t="n"/>
@@ -17539,6 +17823,7 @@
       <c r="U280" s="39" t="n"/>
       <c r="V280" s="38" t="n"/>
       <c r="W280" s="37" t="n"/>
+      <c r="X280" s="36" t="n"/>
     </row>
     <row r="281" ht="28" customHeight="1">
       <c r="A281" s="36" t="n"/>
@@ -17564,6 +17849,7 @@
       <c r="U281" s="39" t="n"/>
       <c r="V281" s="38" t="n"/>
       <c r="W281" s="37" t="n"/>
+      <c r="X281" s="36" t="n"/>
     </row>
     <row r="282" ht="28" customHeight="1">
       <c r="A282" s="36" t="n"/>
@@ -17589,6 +17875,7 @@
       <c r="U282" s="39" t="n"/>
       <c r="V282" s="38" t="n"/>
       <c r="W282" s="37" t="n"/>
+      <c r="X282" s="36" t="n"/>
     </row>
     <row r="283" ht="28" customHeight="1">
       <c r="A283" s="36" t="n"/>
@@ -17614,6 +17901,7 @@
       <c r="U283" s="39" t="n"/>
       <c r="V283" s="38" t="n"/>
       <c r="W283" s="37" t="n"/>
+      <c r="X283" s="36" t="n"/>
     </row>
     <row r="284" ht="28" customHeight="1">
       <c r="A284" s="36" t="n"/>
@@ -17639,6 +17927,7 @@
       <c r="U284" s="39" t="n"/>
       <c r="V284" s="38" t="n"/>
       <c r="W284" s="37" t="n"/>
+      <c r="X284" s="36" t="n"/>
     </row>
     <row r="285" ht="28" customHeight="1">
       <c r="A285" s="36" t="n"/>
@@ -17664,6 +17953,7 @@
       <c r="U285" s="39" t="n"/>
       <c r="V285" s="38" t="n"/>
       <c r="W285" s="37" t="n"/>
+      <c r="X285" s="36" t="n"/>
     </row>
     <row r="286" ht="28" customHeight="1">
       <c r="A286" s="36" t="n"/>
@@ -17689,6 +17979,7 @@
       <c r="U286" s="39" t="n"/>
       <c r="V286" s="38" t="n"/>
       <c r="W286" s="37" t="n"/>
+      <c r="X286" s="36" t="n"/>
     </row>
     <row r="287" ht="28" customHeight="1">
       <c r="A287" s="36" t="n"/>
@@ -17714,6 +18005,7 @@
       <c r="U287" s="39" t="n"/>
       <c r="V287" s="38" t="n"/>
       <c r="W287" s="37" t="n"/>
+      <c r="X287" s="36" t="n"/>
     </row>
     <row r="288" ht="28" customHeight="1">
       <c r="A288" s="36" t="n"/>
@@ -17739,6 +18031,7 @@
       <c r="U288" s="39" t="n"/>
       <c r="V288" s="38" t="n"/>
       <c r="W288" s="37" t="n"/>
+      <c r="X288" s="36" t="n"/>
     </row>
     <row r="289" ht="28" customHeight="1">
       <c r="A289" s="36" t="n"/>
@@ -17764,6 +18057,7 @@
       <c r="U289" s="39" t="n"/>
       <c r="V289" s="38" t="n"/>
       <c r="W289" s="37" t="n"/>
+      <c r="X289" s="36" t="n"/>
     </row>
     <row r="290" ht="28" customHeight="1">
       <c r="A290" s="36" t="n"/>
@@ -17789,6 +18083,7 @@
       <c r="U290" s="39" t="n"/>
       <c r="V290" s="38" t="n"/>
       <c r="W290" s="37" t="n"/>
+      <c r="X290" s="36" t="n"/>
     </row>
     <row r="291" ht="28" customHeight="1">
       <c r="A291" s="36" t="n"/>
@@ -17814,6 +18109,7 @@
       <c r="U291" s="39" t="n"/>
       <c r="V291" s="38" t="n"/>
       <c r="W291" s="37" t="n"/>
+      <c r="X291" s="36" t="n"/>
     </row>
     <row r="292" ht="28" customHeight="1">
       <c r="A292" s="36" t="n"/>
@@ -17839,6 +18135,7 @@
       <c r="U292" s="39" t="n"/>
       <c r="V292" s="38" t="n"/>
       <c r="W292" s="37" t="n"/>
+      <c r="X292" s="36" t="n"/>
     </row>
     <row r="293" ht="28" customHeight="1">
       <c r="A293" s="36" t="n"/>
@@ -17864,6 +18161,7 @@
       <c r="U293" s="39" t="n"/>
       <c r="V293" s="38" t="n"/>
       <c r="W293" s="37" t="n"/>
+      <c r="X293" s="36" t="n"/>
     </row>
     <row r="294" ht="28" customHeight="1">
       <c r="A294" s="36" t="n"/>
@@ -17889,6 +18187,7 @@
       <c r="U294" s="39" t="n"/>
       <c r="V294" s="38" t="n"/>
       <c r="W294" s="37" t="n"/>
+      <c r="X294" s="36" t="n"/>
     </row>
     <row r="295" ht="28" customHeight="1">
       <c r="A295" s="36" t="n"/>
@@ -17914,6 +18213,7 @@
       <c r="U295" s="39" t="n"/>
       <c r="V295" s="38" t="n"/>
       <c r="W295" s="37" t="n"/>
+      <c r="X295" s="36" t="n"/>
     </row>
     <row r="296" ht="28" customHeight="1">
       <c r="A296" s="36" t="n"/>
@@ -17939,6 +18239,7 @@
       <c r="U296" s="39" t="n"/>
       <c r="V296" s="38" t="n"/>
       <c r="W296" s="37" t="n"/>
+      <c r="X296" s="36" t="n"/>
     </row>
     <row r="297" ht="28" customHeight="1">
       <c r="A297" s="36" t="n"/>
@@ -17964,6 +18265,7 @@
       <c r="U297" s="39" t="n"/>
       <c r="V297" s="38" t="n"/>
       <c r="W297" s="37" t="n"/>
+      <c r="X297" s="36" t="n"/>
     </row>
     <row r="298" ht="28" customHeight="1">
       <c r="A298" s="36" t="n"/>
@@ -17989,6 +18291,7 @@
       <c r="U298" s="39" t="n"/>
       <c r="V298" s="38" t="n"/>
       <c r="W298" s="37" t="n"/>
+      <c r="X298" s="36" t="n"/>
     </row>
     <row r="299" ht="28" customHeight="1">
       <c r="A299" s="36" t="n"/>
@@ -18014,6 +18317,7 @@
       <c r="U299" s="39" t="n"/>
       <c r="V299" s="38" t="n"/>
       <c r="W299" s="37" t="n"/>
+      <c r="X299" s="36" t="n"/>
     </row>
     <row r="300" ht="28" customHeight="1">
       <c r="A300" s="36" t="n"/>
@@ -18039,6 +18343,7 @@
       <c r="U300" s="39" t="n"/>
       <c r="V300" s="38" t="n"/>
       <c r="W300" s="37" t="n"/>
+      <c r="X300" s="36" t="n"/>
     </row>
     <row r="301" ht="28" customHeight="1">
       <c r="A301" s="36" t="n"/>
@@ -18064,6 +18369,7 @@
       <c r="U301" s="39" t="n"/>
       <c r="V301" s="38" t="n"/>
       <c r="W301" s="37" t="n"/>
+      <c r="X301" s="36" t="n"/>
     </row>
     <row r="302" ht="28" customHeight="1">
       <c r="A302" s="36" t="n"/>
@@ -18089,6 +18395,7 @@
       <c r="U302" s="39" t="n"/>
       <c r="V302" s="38" t="n"/>
       <c r="W302" s="37" t="n"/>
+      <c r="X302" s="36" t="n"/>
     </row>
     <row r="303" ht="28" customHeight="1">
       <c r="A303" s="36" t="n"/>
@@ -18114,9 +18421,10 @@
       <c r="U303" s="39" t="n"/>
       <c r="V303" s="38" t="n"/>
       <c r="W303" s="37" t="n"/>
+      <c r="X303" s="36" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:W303"/>
+  <autoFilter ref="A3:X303"/>
   <conditionalFormatting sqref="G4:G303">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="3">
       <formula>"مفتوح"</formula>
@@ -18125,7 +18433,7 @@
       <formula>"مقفّل"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:W303">
+  <conditionalFormatting sqref="A4:X303">
     <cfRule type="expression" priority="3" dxfId="2">
       <formula>AND(MOD(ROW(),2)=1,$A4&lt;&gt;"")</formula>
     </cfRule>
@@ -18147,7 +18455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J303"/>
+  <dimension ref="A1:K303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -18160,6 +18468,7 @@
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col hidden="1" width="12" customWidth="1" min="10" max="10"/>
+    <col hidden="1" width="15" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="44" customHeight="1">
@@ -18177,6 +18486,7 @@
       <c r="H1" s="48" t="n"/>
       <c r="I1" s="48" t="n"/>
       <c r="J1" s="48" t="n"/>
+      <c r="K1" s="48" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -18193,6 +18503,7 @@
       <c r="H2" s="33" t="n"/>
       <c r="I2" s="33" t="n"/>
       <c r="J2" s="33" t="n"/>
+      <c r="K2" s="33" t="n"/>
     </row>
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
@@ -18245,6 +18556,11 @@
           <t>الإصدار</t>
         </is>
       </c>
+      <c r="K3" s="34" t="inlineStr">
+        <is>
+          <t>مفتاح عدم التكرار</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="36" t="inlineStr">
@@ -18287,6 +18603,7 @@
       <c r="J4" s="37" t="n">
         <v>1</v>
       </c>
+      <c r="K4" s="36" t="n"/>
     </row>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="36" t="inlineStr">
@@ -18329,6 +18646,7 @@
       <c r="J5" s="37" t="n">
         <v>1</v>
       </c>
+      <c r="K5" s="36" t="n"/>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="36" t="inlineStr">
@@ -18371,6 +18689,7 @@
       <c r="J6" s="37" t="n">
         <v>1</v>
       </c>
+      <c r="K6" s="36" t="n"/>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="36" t="inlineStr">
@@ -18413,6 +18732,7 @@
       <c r="J7" s="37" t="n">
         <v>1</v>
       </c>
+      <c r="K7" s="36" t="n"/>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="36" t="inlineStr">
@@ -18455,6 +18775,7 @@
       <c r="J8" s="37" t="n">
         <v>1</v>
       </c>
+      <c r="K8" s="36" t="n"/>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="36" t="inlineStr">
@@ -18497,6 +18818,7 @@
       <c r="J9" s="37" t="n">
         <v>1</v>
       </c>
+      <c r="K9" s="36" t="n"/>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="36" t="inlineStr">
@@ -18539,6 +18861,7 @@
       <c r="J10" s="37" t="n">
         <v>1</v>
       </c>
+      <c r="K10" s="36" t="n"/>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="36" t="inlineStr">
@@ -18581,6 +18904,7 @@
       <c r="J11" s="37" t="n">
         <v>1</v>
       </c>
+      <c r="K11" s="36" t="n"/>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="36" t="inlineStr">
@@ -18623,6 +18947,7 @@
       <c r="J12" s="37" t="n">
         <v>1</v>
       </c>
+      <c r="K12" s="36" t="n"/>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="36" t="inlineStr">
@@ -18665,6 +18990,7 @@
       <c r="J13" s="37" t="n">
         <v>1</v>
       </c>
+      <c r="K13" s="36" t="n"/>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="36" t="inlineStr">
@@ -18707,6 +19033,7 @@
       <c r="J14" s="37" t="n">
         <v>1</v>
       </c>
+      <c r="K14" s="36" t="n"/>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="36" t="inlineStr">
@@ -18749,6 +19076,7 @@
       <c r="J15" s="37" t="n">
         <v>1</v>
       </c>
+      <c r="K15" s="36" t="n"/>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="36" t="n"/>
@@ -18761,6 +19089,7 @@
       <c r="H16" s="39" t="n"/>
       <c r="I16" s="38" t="n"/>
       <c r="J16" s="37" t="n"/>
+      <c r="K16" s="36" t="n"/>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="36" t="n"/>
@@ -18773,6 +19102,7 @@
       <c r="H17" s="39" t="n"/>
       <c r="I17" s="38" t="n"/>
       <c r="J17" s="37" t="n"/>
+      <c r="K17" s="36" t="n"/>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="36" t="n"/>
@@ -18785,6 +19115,7 @@
       <c r="H18" s="39" t="n"/>
       <c r="I18" s="38" t="n"/>
       <c r="J18" s="37" t="n"/>
+      <c r="K18" s="36" t="n"/>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="36" t="n"/>
@@ -18797,6 +19128,7 @@
       <c r="H19" s="39" t="n"/>
       <c r="I19" s="38" t="n"/>
       <c r="J19" s="37" t="n"/>
+      <c r="K19" s="36" t="n"/>
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="36" t="n"/>
@@ -18809,6 +19141,7 @@
       <c r="H20" s="39" t="n"/>
       <c r="I20" s="38" t="n"/>
       <c r="J20" s="37" t="n"/>
+      <c r="K20" s="36" t="n"/>
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="36" t="n"/>
@@ -18821,6 +19154,7 @@
       <c r="H21" s="39" t="n"/>
       <c r="I21" s="38" t="n"/>
       <c r="J21" s="37" t="n"/>
+      <c r="K21" s="36" t="n"/>
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="36" t="n"/>
@@ -18833,6 +19167,7 @@
       <c r="H22" s="39" t="n"/>
       <c r="I22" s="38" t="n"/>
       <c r="J22" s="37" t="n"/>
+      <c r="K22" s="36" t="n"/>
     </row>
     <row r="23" ht="28" customHeight="1">
       <c r="A23" s="36" t="n"/>
@@ -18845,6 +19180,7 @@
       <c r="H23" s="39" t="n"/>
       <c r="I23" s="38" t="n"/>
       <c r="J23" s="37" t="n"/>
+      <c r="K23" s="36" t="n"/>
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="36" t="n"/>
@@ -18857,6 +19193,7 @@
       <c r="H24" s="39" t="n"/>
       <c r="I24" s="38" t="n"/>
       <c r="J24" s="37" t="n"/>
+      <c r="K24" s="36" t="n"/>
     </row>
     <row r="25" ht="28" customHeight="1">
       <c r="A25" s="36" t="n"/>
@@ -18869,6 +19206,7 @@
       <c r="H25" s="39" t="n"/>
       <c r="I25" s="38" t="n"/>
       <c r="J25" s="37" t="n"/>
+      <c r="K25" s="36" t="n"/>
     </row>
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="36" t="n"/>
@@ -18881,6 +19219,7 @@
       <c r="H26" s="39" t="n"/>
       <c r="I26" s="38" t="n"/>
       <c r="J26" s="37" t="n"/>
+      <c r="K26" s="36" t="n"/>
     </row>
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="36" t="n"/>
@@ -18893,6 +19232,7 @@
       <c r="H27" s="39" t="n"/>
       <c r="I27" s="38" t="n"/>
       <c r="J27" s="37" t="n"/>
+      <c r="K27" s="36" t="n"/>
     </row>
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="36" t="n"/>
@@ -18905,6 +19245,7 @@
       <c r="H28" s="39" t="n"/>
       <c r="I28" s="38" t="n"/>
       <c r="J28" s="37" t="n"/>
+      <c r="K28" s="36" t="n"/>
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="36" t="n"/>
@@ -18917,6 +19258,7 @@
       <c r="H29" s="39" t="n"/>
       <c r="I29" s="38" t="n"/>
       <c r="J29" s="37" t="n"/>
+      <c r="K29" s="36" t="n"/>
     </row>
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="36" t="n"/>
@@ -18929,6 +19271,7 @@
       <c r="H30" s="39" t="n"/>
       <c r="I30" s="38" t="n"/>
       <c r="J30" s="37" t="n"/>
+      <c r="K30" s="36" t="n"/>
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="36" t="n"/>
@@ -18941,6 +19284,7 @@
       <c r="H31" s="39" t="n"/>
       <c r="I31" s="38" t="n"/>
       <c r="J31" s="37" t="n"/>
+      <c r="K31" s="36" t="n"/>
     </row>
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="36" t="n"/>
@@ -18953,6 +19297,7 @@
       <c r="H32" s="39" t="n"/>
       <c r="I32" s="38" t="n"/>
       <c r="J32" s="37" t="n"/>
+      <c r="K32" s="36" t="n"/>
     </row>
     <row r="33" ht="28" customHeight="1">
       <c r="A33" s="36" t="n"/>
@@ -18965,6 +19310,7 @@
       <c r="H33" s="39" t="n"/>
       <c r="I33" s="38" t="n"/>
       <c r="J33" s="37" t="n"/>
+      <c r="K33" s="36" t="n"/>
     </row>
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="36" t="n"/>
@@ -18977,6 +19323,7 @@
       <c r="H34" s="39" t="n"/>
       <c r="I34" s="38" t="n"/>
       <c r="J34" s="37" t="n"/>
+      <c r="K34" s="36" t="n"/>
     </row>
     <row r="35" ht="28" customHeight="1">
       <c r="A35" s="36" t="n"/>
@@ -18989,6 +19336,7 @@
       <c r="H35" s="39" t="n"/>
       <c r="I35" s="38" t="n"/>
       <c r="J35" s="37" t="n"/>
+      <c r="K35" s="36" t="n"/>
     </row>
     <row r="36" ht="28" customHeight="1">
       <c r="A36" s="36" t="n"/>
@@ -19001,6 +19349,7 @@
       <c r="H36" s="39" t="n"/>
       <c r="I36" s="38" t="n"/>
       <c r="J36" s="37" t="n"/>
+      <c r="K36" s="36" t="n"/>
     </row>
     <row r="37" ht="28" customHeight="1">
       <c r="A37" s="36" t="n"/>
@@ -19013,6 +19362,7 @@
       <c r="H37" s="39" t="n"/>
       <c r="I37" s="38" t="n"/>
       <c r="J37" s="37" t="n"/>
+      <c r="K37" s="36" t="n"/>
     </row>
     <row r="38" ht="28" customHeight="1">
       <c r="A38" s="36" t="n"/>
@@ -19025,6 +19375,7 @@
       <c r="H38" s="39" t="n"/>
       <c r="I38" s="38" t="n"/>
       <c r="J38" s="37" t="n"/>
+      <c r="K38" s="36" t="n"/>
     </row>
     <row r="39" ht="28" customHeight="1">
       <c r="A39" s="36" t="n"/>
@@ -19037,6 +19388,7 @@
       <c r="H39" s="39" t="n"/>
       <c r="I39" s="38" t="n"/>
       <c r="J39" s="37" t="n"/>
+      <c r="K39" s="36" t="n"/>
     </row>
     <row r="40" ht="28" customHeight="1">
       <c r="A40" s="36" t="n"/>
@@ -19049,6 +19401,7 @@
       <c r="H40" s="39" t="n"/>
       <c r="I40" s="38" t="n"/>
       <c r="J40" s="37" t="n"/>
+      <c r="K40" s="36" t="n"/>
     </row>
     <row r="41" ht="28" customHeight="1">
       <c r="A41" s="36" t="n"/>
@@ -19061,6 +19414,7 @@
       <c r="H41" s="39" t="n"/>
       <c r="I41" s="38" t="n"/>
       <c r="J41" s="37" t="n"/>
+      <c r="K41" s="36" t="n"/>
     </row>
     <row r="42" ht="28" customHeight="1">
       <c r="A42" s="36" t="n"/>
@@ -19073,6 +19427,7 @@
       <c r="H42" s="39" t="n"/>
       <c r="I42" s="38" t="n"/>
       <c r="J42" s="37" t="n"/>
+      <c r="K42" s="36" t="n"/>
     </row>
     <row r="43" ht="28" customHeight="1">
       <c r="A43" s="36" t="n"/>
@@ -19085,6 +19440,7 @@
       <c r="H43" s="39" t="n"/>
       <c r="I43" s="38" t="n"/>
       <c r="J43" s="37" t="n"/>
+      <c r="K43" s="36" t="n"/>
     </row>
     <row r="44" ht="28" customHeight="1">
       <c r="A44" s="36" t="n"/>
@@ -19097,6 +19453,7 @@
       <c r="H44" s="39" t="n"/>
       <c r="I44" s="38" t="n"/>
       <c r="J44" s="37" t="n"/>
+      <c r="K44" s="36" t="n"/>
     </row>
     <row r="45" ht="28" customHeight="1">
       <c r="A45" s="36" t="n"/>
@@ -19109,6 +19466,7 @@
       <c r="H45" s="39" t="n"/>
       <c r="I45" s="38" t="n"/>
       <c r="J45" s="37" t="n"/>
+      <c r="K45" s="36" t="n"/>
     </row>
     <row r="46" ht="28" customHeight="1">
       <c r="A46" s="36" t="n"/>
@@ -19121,6 +19479,7 @@
       <c r="H46" s="39" t="n"/>
       <c r="I46" s="38" t="n"/>
       <c r="J46" s="37" t="n"/>
+      <c r="K46" s="36" t="n"/>
     </row>
     <row r="47" ht="28" customHeight="1">
       <c r="A47" s="36" t="n"/>
@@ -19133,6 +19492,7 @@
       <c r="H47" s="39" t="n"/>
       <c r="I47" s="38" t="n"/>
       <c r="J47" s="37" t="n"/>
+      <c r="K47" s="36" t="n"/>
     </row>
     <row r="48" ht="28" customHeight="1">
       <c r="A48" s="36" t="n"/>
@@ -19145,6 +19505,7 @@
       <c r="H48" s="39" t="n"/>
       <c r="I48" s="38" t="n"/>
       <c r="J48" s="37" t="n"/>
+      <c r="K48" s="36" t="n"/>
     </row>
     <row r="49" ht="28" customHeight="1">
       <c r="A49" s="36" t="n"/>
@@ -19157,6 +19518,7 @@
       <c r="H49" s="39" t="n"/>
       <c r="I49" s="38" t="n"/>
       <c r="J49" s="37" t="n"/>
+      <c r="K49" s="36" t="n"/>
     </row>
     <row r="50" ht="28" customHeight="1">
       <c r="A50" s="36" t="n"/>
@@ -19169,6 +19531,7 @@
       <c r="H50" s="39" t="n"/>
       <c r="I50" s="38" t="n"/>
       <c r="J50" s="37" t="n"/>
+      <c r="K50" s="36" t="n"/>
     </row>
     <row r="51" ht="28" customHeight="1">
       <c r="A51" s="36" t="n"/>
@@ -19181,6 +19544,7 @@
       <c r="H51" s="39" t="n"/>
       <c r="I51" s="38" t="n"/>
       <c r="J51" s="37" t="n"/>
+      <c r="K51" s="36" t="n"/>
     </row>
     <row r="52" ht="28" customHeight="1">
       <c r="A52" s="36" t="n"/>
@@ -19193,6 +19557,7 @@
       <c r="H52" s="39" t="n"/>
       <c r="I52" s="38" t="n"/>
       <c r="J52" s="37" t="n"/>
+      <c r="K52" s="36" t="n"/>
     </row>
     <row r="53" ht="28" customHeight="1">
       <c r="A53" s="36" t="n"/>
@@ -19205,6 +19570,7 @@
       <c r="H53" s="39" t="n"/>
       <c r="I53" s="38" t="n"/>
       <c r="J53" s="37" t="n"/>
+      <c r="K53" s="36" t="n"/>
     </row>
     <row r="54" ht="28" customHeight="1">
       <c r="A54" s="36" t="n"/>
@@ -19217,6 +19583,7 @@
       <c r="H54" s="39" t="n"/>
       <c r="I54" s="38" t="n"/>
       <c r="J54" s="37" t="n"/>
+      <c r="K54" s="36" t="n"/>
     </row>
     <row r="55" ht="28" customHeight="1">
       <c r="A55" s="36" t="n"/>
@@ -19229,6 +19596,7 @@
       <c r="H55" s="39" t="n"/>
       <c r="I55" s="38" t="n"/>
       <c r="J55" s="37" t="n"/>
+      <c r="K55" s="36" t="n"/>
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="36" t="n"/>
@@ -19241,6 +19609,7 @@
       <c r="H56" s="39" t="n"/>
       <c r="I56" s="38" t="n"/>
       <c r="J56" s="37" t="n"/>
+      <c r="K56" s="36" t="n"/>
     </row>
     <row r="57" ht="28" customHeight="1">
       <c r="A57" s="36" t="n"/>
@@ -19253,6 +19622,7 @@
       <c r="H57" s="39" t="n"/>
       <c r="I57" s="38" t="n"/>
       <c r="J57" s="37" t="n"/>
+      <c r="K57" s="36" t="n"/>
     </row>
     <row r="58" ht="28" customHeight="1">
       <c r="A58" s="36" t="n"/>
@@ -19265,6 +19635,7 @@
       <c r="H58" s="39" t="n"/>
       <c r="I58" s="38" t="n"/>
       <c r="J58" s="37" t="n"/>
+      <c r="K58" s="36" t="n"/>
     </row>
     <row r="59" ht="28" customHeight="1">
       <c r="A59" s="36" t="n"/>
@@ -19277,6 +19648,7 @@
       <c r="H59" s="39" t="n"/>
       <c r="I59" s="38" t="n"/>
       <c r="J59" s="37" t="n"/>
+      <c r="K59" s="36" t="n"/>
     </row>
     <row r="60" ht="28" customHeight="1">
       <c r="A60" s="36" t="n"/>
@@ -19289,6 +19661,7 @@
       <c r="H60" s="39" t="n"/>
       <c r="I60" s="38" t="n"/>
       <c r="J60" s="37" t="n"/>
+      <c r="K60" s="36" t="n"/>
     </row>
     <row r="61" ht="28" customHeight="1">
       <c r="A61" s="36" t="n"/>
@@ -19301,6 +19674,7 @@
       <c r="H61" s="39" t="n"/>
       <c r="I61" s="38" t="n"/>
       <c r="J61" s="37" t="n"/>
+      <c r="K61" s="36" t="n"/>
     </row>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="36" t="n"/>
@@ -19313,6 +19687,7 @@
       <c r="H62" s="39" t="n"/>
       <c r="I62" s="38" t="n"/>
       <c r="J62" s="37" t="n"/>
+      <c r="K62" s="36" t="n"/>
     </row>
     <row r="63" ht="28" customHeight="1">
       <c r="A63" s="36" t="n"/>
@@ -19325,6 +19700,7 @@
       <c r="H63" s="39" t="n"/>
       <c r="I63" s="38" t="n"/>
       <c r="J63" s="37" t="n"/>
+      <c r="K63" s="36" t="n"/>
     </row>
     <row r="64" ht="28" customHeight="1">
       <c r="A64" s="36" t="n"/>
@@ -19337,6 +19713,7 @@
       <c r="H64" s="39" t="n"/>
       <c r="I64" s="38" t="n"/>
       <c r="J64" s="37" t="n"/>
+      <c r="K64" s="36" t="n"/>
     </row>
     <row r="65" ht="28" customHeight="1">
       <c r="A65" s="36" t="n"/>
@@ -19349,6 +19726,7 @@
       <c r="H65" s="39" t="n"/>
       <c r="I65" s="38" t="n"/>
       <c r="J65" s="37" t="n"/>
+      <c r="K65" s="36" t="n"/>
     </row>
     <row r="66" ht="28" customHeight="1">
       <c r="A66" s="36" t="n"/>
@@ -19361,6 +19739,7 @@
       <c r="H66" s="39" t="n"/>
       <c r="I66" s="38" t="n"/>
       <c r="J66" s="37" t="n"/>
+      <c r="K66" s="36" t="n"/>
     </row>
     <row r="67" ht="28" customHeight="1">
       <c r="A67" s="36" t="n"/>
@@ -19373,6 +19752,7 @@
       <c r="H67" s="39" t="n"/>
       <c r="I67" s="38" t="n"/>
       <c r="J67" s="37" t="n"/>
+      <c r="K67" s="36" t="n"/>
     </row>
     <row r="68" ht="28" customHeight="1">
       <c r="A68" s="36" t="n"/>
@@ -19385,6 +19765,7 @@
       <c r="H68" s="39" t="n"/>
       <c r="I68" s="38" t="n"/>
       <c r="J68" s="37" t="n"/>
+      <c r="K68" s="36" t="n"/>
     </row>
     <row r="69" ht="28" customHeight="1">
       <c r="A69" s="36" t="n"/>
@@ -19397,6 +19778,7 @@
       <c r="H69" s="39" t="n"/>
       <c r="I69" s="38" t="n"/>
       <c r="J69" s="37" t="n"/>
+      <c r="K69" s="36" t="n"/>
     </row>
     <row r="70" ht="28" customHeight="1">
       <c r="A70" s="36" t="n"/>
@@ -19409,6 +19791,7 @@
       <c r="H70" s="39" t="n"/>
       <c r="I70" s="38" t="n"/>
       <c r="J70" s="37" t="n"/>
+      <c r="K70" s="36" t="n"/>
     </row>
     <row r="71" ht="28" customHeight="1">
       <c r="A71" s="36" t="n"/>
@@ -19421,6 +19804,7 @@
       <c r="H71" s="39" t="n"/>
       <c r="I71" s="38" t="n"/>
       <c r="J71" s="37" t="n"/>
+      <c r="K71" s="36" t="n"/>
     </row>
     <row r="72" ht="28" customHeight="1">
       <c r="A72" s="36" t="n"/>
@@ -19433,6 +19817,7 @@
       <c r="H72" s="39" t="n"/>
       <c r="I72" s="38" t="n"/>
       <c r="J72" s="37" t="n"/>
+      <c r="K72" s="36" t="n"/>
     </row>
     <row r="73" ht="28" customHeight="1">
       <c r="A73" s="36" t="n"/>
@@ -19445,6 +19830,7 @@
       <c r="H73" s="39" t="n"/>
       <c r="I73" s="38" t="n"/>
       <c r="J73" s="37" t="n"/>
+      <c r="K73" s="36" t="n"/>
     </row>
     <row r="74" ht="28" customHeight="1">
       <c r="A74" s="36" t="n"/>
@@ -19457,6 +19843,7 @@
       <c r="H74" s="39" t="n"/>
       <c r="I74" s="38" t="n"/>
       <c r="J74" s="37" t="n"/>
+      <c r="K74" s="36" t="n"/>
     </row>
     <row r="75" ht="28" customHeight="1">
       <c r="A75" s="36" t="n"/>
@@ -19469,6 +19856,7 @@
       <c r="H75" s="39" t="n"/>
       <c r="I75" s="38" t="n"/>
       <c r="J75" s="37" t="n"/>
+      <c r="K75" s="36" t="n"/>
     </row>
     <row r="76" ht="28" customHeight="1">
       <c r="A76" s="36" t="n"/>
@@ -19481,6 +19869,7 @@
       <c r="H76" s="39" t="n"/>
       <c r="I76" s="38" t="n"/>
       <c r="J76" s="37" t="n"/>
+      <c r="K76" s="36" t="n"/>
     </row>
     <row r="77" ht="28" customHeight="1">
       <c r="A77" s="36" t="n"/>
@@ -19493,6 +19882,7 @@
       <c r="H77" s="39" t="n"/>
       <c r="I77" s="38" t="n"/>
       <c r="J77" s="37" t="n"/>
+      <c r="K77" s="36" t="n"/>
     </row>
     <row r="78" ht="28" customHeight="1">
       <c r="A78" s="36" t="n"/>
@@ -19505,6 +19895,7 @@
       <c r="H78" s="39" t="n"/>
       <c r="I78" s="38" t="n"/>
       <c r="J78" s="37" t="n"/>
+      <c r="K78" s="36" t="n"/>
     </row>
     <row r="79" ht="28" customHeight="1">
       <c r="A79" s="36" t="n"/>
@@ -19517,6 +19908,7 @@
       <c r="H79" s="39" t="n"/>
       <c r="I79" s="38" t="n"/>
       <c r="J79" s="37" t="n"/>
+      <c r="K79" s="36" t="n"/>
     </row>
     <row r="80" ht="28" customHeight="1">
       <c r="A80" s="36" t="n"/>
@@ -19529,6 +19921,7 @@
       <c r="H80" s="39" t="n"/>
       <c r="I80" s="38" t="n"/>
       <c r="J80" s="37" t="n"/>
+      <c r="K80" s="36" t="n"/>
     </row>
     <row r="81" ht="28" customHeight="1">
       <c r="A81" s="36" t="n"/>
@@ -19541,6 +19934,7 @@
       <c r="H81" s="39" t="n"/>
       <c r="I81" s="38" t="n"/>
       <c r="J81" s="37" t="n"/>
+      <c r="K81" s="36" t="n"/>
     </row>
     <row r="82" ht="28" customHeight="1">
       <c r="A82" s="36" t="n"/>
@@ -19553,6 +19947,7 @@
       <c r="H82" s="39" t="n"/>
       <c r="I82" s="38" t="n"/>
       <c r="J82" s="37" t="n"/>
+      <c r="K82" s="36" t="n"/>
     </row>
     <row r="83" ht="28" customHeight="1">
       <c r="A83" s="36" t="n"/>
@@ -19565,6 +19960,7 @@
       <c r="H83" s="39" t="n"/>
       <c r="I83" s="38" t="n"/>
       <c r="J83" s="37" t="n"/>
+      <c r="K83" s="36" t="n"/>
     </row>
     <row r="84" ht="28" customHeight="1">
       <c r="A84" s="36" t="n"/>
@@ -19577,6 +19973,7 @@
       <c r="H84" s="39" t="n"/>
       <c r="I84" s="38" t="n"/>
       <c r="J84" s="37" t="n"/>
+      <c r="K84" s="36" t="n"/>
     </row>
     <row r="85" ht="28" customHeight="1">
       <c r="A85" s="36" t="n"/>
@@ -19589,6 +19986,7 @@
       <c r="H85" s="39" t="n"/>
       <c r="I85" s="38" t="n"/>
       <c r="J85" s="37" t="n"/>
+      <c r="K85" s="36" t="n"/>
     </row>
     <row r="86" ht="28" customHeight="1">
       <c r="A86" s="36" t="n"/>
@@ -19601,6 +19999,7 @@
       <c r="H86" s="39" t="n"/>
       <c r="I86" s="38" t="n"/>
       <c r="J86" s="37" t="n"/>
+      <c r="K86" s="36" t="n"/>
     </row>
     <row r="87" ht="28" customHeight="1">
       <c r="A87" s="36" t="n"/>
@@ -19613,6 +20012,7 @@
       <c r="H87" s="39" t="n"/>
       <c r="I87" s="38" t="n"/>
       <c r="J87" s="37" t="n"/>
+      <c r="K87" s="36" t="n"/>
     </row>
     <row r="88" ht="28" customHeight="1">
       <c r="A88" s="36" t="n"/>
@@ -19625,6 +20025,7 @@
       <c r="H88" s="39" t="n"/>
       <c r="I88" s="38" t="n"/>
       <c r="J88" s="37" t="n"/>
+      <c r="K88" s="36" t="n"/>
     </row>
     <row r="89" ht="28" customHeight="1">
       <c r="A89" s="36" t="n"/>
@@ -19637,6 +20038,7 @@
       <c r="H89" s="39" t="n"/>
       <c r="I89" s="38" t="n"/>
       <c r="J89" s="37" t="n"/>
+      <c r="K89" s="36" t="n"/>
     </row>
     <row r="90" ht="28" customHeight="1">
       <c r="A90" s="36" t="n"/>
@@ -19649,6 +20051,7 @@
       <c r="H90" s="39" t="n"/>
       <c r="I90" s="38" t="n"/>
       <c r="J90" s="37" t="n"/>
+      <c r="K90" s="36" t="n"/>
     </row>
     <row r="91" ht="28" customHeight="1">
       <c r="A91" s="36" t="n"/>
@@ -19661,6 +20064,7 @@
       <c r="H91" s="39" t="n"/>
       <c r="I91" s="38" t="n"/>
       <c r="J91" s="37" t="n"/>
+      <c r="K91" s="36" t="n"/>
     </row>
     <row r="92" ht="28" customHeight="1">
       <c r="A92" s="36" t="n"/>
@@ -19673,6 +20077,7 @@
       <c r="H92" s="39" t="n"/>
       <c r="I92" s="38" t="n"/>
       <c r="J92" s="37" t="n"/>
+      <c r="K92" s="36" t="n"/>
     </row>
     <row r="93" ht="28" customHeight="1">
       <c r="A93" s="36" t="n"/>
@@ -19685,6 +20090,7 @@
       <c r="H93" s="39" t="n"/>
       <c r="I93" s="38" t="n"/>
       <c r="J93" s="37" t="n"/>
+      <c r="K93" s="36" t="n"/>
     </row>
     <row r="94" ht="28" customHeight="1">
       <c r="A94" s="36" t="n"/>
@@ -19697,6 +20103,7 @@
       <c r="H94" s="39" t="n"/>
       <c r="I94" s="38" t="n"/>
       <c r="J94" s="37" t="n"/>
+      <c r="K94" s="36" t="n"/>
     </row>
     <row r="95" ht="28" customHeight="1">
       <c r="A95" s="36" t="n"/>
@@ -19709,6 +20116,7 @@
       <c r="H95" s="39" t="n"/>
       <c r="I95" s="38" t="n"/>
       <c r="J95" s="37" t="n"/>
+      <c r="K95" s="36" t="n"/>
     </row>
     <row r="96" ht="28" customHeight="1">
       <c r="A96" s="36" t="n"/>
@@ -19721,6 +20129,7 @@
       <c r="H96" s="39" t="n"/>
       <c r="I96" s="38" t="n"/>
       <c r="J96" s="37" t="n"/>
+      <c r="K96" s="36" t="n"/>
     </row>
     <row r="97" ht="28" customHeight="1">
       <c r="A97" s="36" t="n"/>
@@ -19733,6 +20142,7 @@
       <c r="H97" s="39" t="n"/>
       <c r="I97" s="38" t="n"/>
       <c r="J97" s="37" t="n"/>
+      <c r="K97" s="36" t="n"/>
     </row>
     <row r="98" ht="28" customHeight="1">
       <c r="A98" s="36" t="n"/>
@@ -19745,6 +20155,7 @@
       <c r="H98" s="39" t="n"/>
       <c r="I98" s="38" t="n"/>
       <c r="J98" s="37" t="n"/>
+      <c r="K98" s="36" t="n"/>
     </row>
     <row r="99" ht="28" customHeight="1">
       <c r="A99" s="36" t="n"/>
@@ -19757,6 +20168,7 @@
       <c r="H99" s="39" t="n"/>
       <c r="I99" s="38" t="n"/>
       <c r="J99" s="37" t="n"/>
+      <c r="K99" s="36" t="n"/>
     </row>
     <row r="100" ht="28" customHeight="1">
       <c r="A100" s="36" t="n"/>
@@ -19769,6 +20181,7 @@
       <c r="H100" s="39" t="n"/>
       <c r="I100" s="38" t="n"/>
       <c r="J100" s="37" t="n"/>
+      <c r="K100" s="36" t="n"/>
     </row>
     <row r="101" ht="28" customHeight="1">
       <c r="A101" s="36" t="n"/>
@@ -19781,6 +20194,7 @@
       <c r="H101" s="39" t="n"/>
       <c r="I101" s="38" t="n"/>
       <c r="J101" s="37" t="n"/>
+      <c r="K101" s="36" t="n"/>
     </row>
     <row r="102" ht="28" customHeight="1">
       <c r="A102" s="36" t="n"/>
@@ -19793,6 +20207,7 @@
       <c r="H102" s="39" t="n"/>
       <c r="I102" s="38" t="n"/>
       <c r="J102" s="37" t="n"/>
+      <c r="K102" s="36" t="n"/>
     </row>
     <row r="103" ht="28" customHeight="1">
       <c r="A103" s="36" t="n"/>
@@ -19805,6 +20220,7 @@
       <c r="H103" s="39" t="n"/>
       <c r="I103" s="38" t="n"/>
       <c r="J103" s="37" t="n"/>
+      <c r="K103" s="36" t="n"/>
     </row>
     <row r="104" ht="28" customHeight="1">
       <c r="A104" s="36" t="n"/>
@@ -19817,6 +20233,7 @@
       <c r="H104" s="39" t="n"/>
       <c r="I104" s="38" t="n"/>
       <c r="J104" s="37" t="n"/>
+      <c r="K104" s="36" t="n"/>
     </row>
     <row r="105" ht="28" customHeight="1">
       <c r="A105" s="36" t="n"/>
@@ -19829,6 +20246,7 @@
       <c r="H105" s="39" t="n"/>
       <c r="I105" s="38" t="n"/>
       <c r="J105" s="37" t="n"/>
+      <c r="K105" s="36" t="n"/>
     </row>
     <row r="106" ht="28" customHeight="1">
       <c r="A106" s="36" t="n"/>
@@ -19841,6 +20259,7 @@
       <c r="H106" s="39" t="n"/>
       <c r="I106" s="38" t="n"/>
       <c r="J106" s="37" t="n"/>
+      <c r="K106" s="36" t="n"/>
     </row>
     <row r="107" ht="28" customHeight="1">
       <c r="A107" s="36" t="n"/>
@@ -19853,6 +20272,7 @@
       <c r="H107" s="39" t="n"/>
       <c r="I107" s="38" t="n"/>
       <c r="J107" s="37" t="n"/>
+      <c r="K107" s="36" t="n"/>
     </row>
     <row r="108" ht="28" customHeight="1">
       <c r="A108" s="36" t="n"/>
@@ -19865,6 +20285,7 @@
       <c r="H108" s="39" t="n"/>
       <c r="I108" s="38" t="n"/>
       <c r="J108" s="37" t="n"/>
+      <c r="K108" s="36" t="n"/>
     </row>
     <row r="109" ht="28" customHeight="1">
       <c r="A109" s="36" t="n"/>
@@ -19877,6 +20298,7 @@
       <c r="H109" s="39" t="n"/>
       <c r="I109" s="38" t="n"/>
       <c r="J109" s="37" t="n"/>
+      <c r="K109" s="36" t="n"/>
     </row>
     <row r="110" ht="28" customHeight="1">
       <c r="A110" s="36" t="n"/>
@@ -19889,6 +20311,7 @@
       <c r="H110" s="39" t="n"/>
       <c r="I110" s="38" t="n"/>
       <c r="J110" s="37" t="n"/>
+      <c r="K110" s="36" t="n"/>
     </row>
     <row r="111" ht="28" customHeight="1">
       <c r="A111" s="36" t="n"/>
@@ -19901,6 +20324,7 @@
       <c r="H111" s="39" t="n"/>
       <c r="I111" s="38" t="n"/>
       <c r="J111" s="37" t="n"/>
+      <c r="K111" s="36" t="n"/>
     </row>
     <row r="112" ht="28" customHeight="1">
       <c r="A112" s="36" t="n"/>
@@ -19913,6 +20337,7 @@
       <c r="H112" s="39" t="n"/>
       <c r="I112" s="38" t="n"/>
       <c r="J112" s="37" t="n"/>
+      <c r="K112" s="36" t="n"/>
     </row>
     <row r="113" ht="28" customHeight="1">
       <c r="A113" s="36" t="n"/>
@@ -19925,6 +20350,7 @@
       <c r="H113" s="39" t="n"/>
       <c r="I113" s="38" t="n"/>
       <c r="J113" s="37" t="n"/>
+      <c r="K113" s="36" t="n"/>
     </row>
     <row r="114" ht="28" customHeight="1">
       <c r="A114" s="36" t="n"/>
@@ -19937,6 +20363,7 @@
       <c r="H114" s="39" t="n"/>
       <c r="I114" s="38" t="n"/>
       <c r="J114" s="37" t="n"/>
+      <c r="K114" s="36" t="n"/>
     </row>
     <row r="115" ht="28" customHeight="1">
       <c r="A115" s="36" t="n"/>
@@ -19949,6 +20376,7 @@
       <c r="H115" s="39" t="n"/>
       <c r="I115" s="38" t="n"/>
       <c r="J115" s="37" t="n"/>
+      <c r="K115" s="36" t="n"/>
     </row>
     <row r="116" ht="28" customHeight="1">
       <c r="A116" s="36" t="n"/>
@@ -19961,6 +20389,7 @@
       <c r="H116" s="39" t="n"/>
       <c r="I116" s="38" t="n"/>
       <c r="J116" s="37" t="n"/>
+      <c r="K116" s="36" t="n"/>
     </row>
     <row r="117" ht="28" customHeight="1">
       <c r="A117" s="36" t="n"/>
@@ -19973,6 +20402,7 @@
       <c r="H117" s="39" t="n"/>
       <c r="I117" s="38" t="n"/>
       <c r="J117" s="37" t="n"/>
+      <c r="K117" s="36" t="n"/>
     </row>
     <row r="118" ht="28" customHeight="1">
       <c r="A118" s="36" t="n"/>
@@ -19985,6 +20415,7 @@
       <c r="H118" s="39" t="n"/>
       <c r="I118" s="38" t="n"/>
       <c r="J118" s="37" t="n"/>
+      <c r="K118" s="36" t="n"/>
     </row>
     <row r="119" ht="28" customHeight="1">
       <c r="A119" s="36" t="n"/>
@@ -19997,6 +20428,7 @@
       <c r="H119" s="39" t="n"/>
       <c r="I119" s="38" t="n"/>
       <c r="J119" s="37" t="n"/>
+      <c r="K119" s="36" t="n"/>
     </row>
     <row r="120" ht="28" customHeight="1">
       <c r="A120" s="36" t="n"/>
@@ -20009,6 +20441,7 @@
       <c r="H120" s="39" t="n"/>
       <c r="I120" s="38" t="n"/>
       <c r="J120" s="37" t="n"/>
+      <c r="K120" s="36" t="n"/>
     </row>
     <row r="121" ht="28" customHeight="1">
       <c r="A121" s="36" t="n"/>
@@ -20021,6 +20454,7 @@
       <c r="H121" s="39" t="n"/>
       <c r="I121" s="38" t="n"/>
       <c r="J121" s="37" t="n"/>
+      <c r="K121" s="36" t="n"/>
     </row>
     <row r="122" ht="28" customHeight="1">
       <c r="A122" s="36" t="n"/>
@@ -20033,6 +20467,7 @@
       <c r="H122" s="39" t="n"/>
       <c r="I122" s="38" t="n"/>
       <c r="J122" s="37" t="n"/>
+      <c r="K122" s="36" t="n"/>
     </row>
     <row r="123" ht="28" customHeight="1">
       <c r="A123" s="36" t="n"/>
@@ -20045,6 +20480,7 @@
       <c r="H123" s="39" t="n"/>
       <c r="I123" s="38" t="n"/>
       <c r="J123" s="37" t="n"/>
+      <c r="K123" s="36" t="n"/>
     </row>
     <row r="124" ht="28" customHeight="1">
       <c r="A124" s="36" t="n"/>
@@ -20057,6 +20493,7 @@
       <c r="H124" s="39" t="n"/>
       <c r="I124" s="38" t="n"/>
       <c r="J124" s="37" t="n"/>
+      <c r="K124" s="36" t="n"/>
     </row>
     <row r="125" ht="28" customHeight="1">
       <c r="A125" s="36" t="n"/>
@@ -20069,6 +20506,7 @@
       <c r="H125" s="39" t="n"/>
       <c r="I125" s="38" t="n"/>
       <c r="J125" s="37" t="n"/>
+      <c r="K125" s="36" t="n"/>
     </row>
     <row r="126" ht="28" customHeight="1">
       <c r="A126" s="36" t="n"/>
@@ -20081,6 +20519,7 @@
       <c r="H126" s="39" t="n"/>
       <c r="I126" s="38" t="n"/>
       <c r="J126" s="37" t="n"/>
+      <c r="K126" s="36" t="n"/>
     </row>
     <row r="127" ht="28" customHeight="1">
       <c r="A127" s="36" t="n"/>
@@ -20093,6 +20532,7 @@
       <c r="H127" s="39" t="n"/>
       <c r="I127" s="38" t="n"/>
       <c r="J127" s="37" t="n"/>
+      <c r="K127" s="36" t="n"/>
     </row>
     <row r="128" ht="28" customHeight="1">
       <c r="A128" s="36" t="n"/>
@@ -20105,6 +20545,7 @@
       <c r="H128" s="39" t="n"/>
       <c r="I128" s="38" t="n"/>
       <c r="J128" s="37" t="n"/>
+      <c r="K128" s="36" t="n"/>
     </row>
     <row r="129" ht="28" customHeight="1">
       <c r="A129" s="36" t="n"/>
@@ -20117,6 +20558,7 @@
       <c r="H129" s="39" t="n"/>
       <c r="I129" s="38" t="n"/>
       <c r="J129" s="37" t="n"/>
+      <c r="K129" s="36" t="n"/>
     </row>
     <row r="130" ht="28" customHeight="1">
       <c r="A130" s="36" t="n"/>
@@ -20129,6 +20571,7 @@
       <c r="H130" s="39" t="n"/>
       <c r="I130" s="38" t="n"/>
       <c r="J130" s="37" t="n"/>
+      <c r="K130" s="36" t="n"/>
     </row>
     <row r="131" ht="28" customHeight="1">
       <c r="A131" s="36" t="n"/>
@@ -20141,6 +20584,7 @@
       <c r="H131" s="39" t="n"/>
       <c r="I131" s="38" t="n"/>
       <c r="J131" s="37" t="n"/>
+      <c r="K131" s="36" t="n"/>
     </row>
     <row r="132" ht="28" customHeight="1">
       <c r="A132" s="36" t="n"/>
@@ -20153,6 +20597,7 @@
       <c r="H132" s="39" t="n"/>
       <c r="I132" s="38" t="n"/>
       <c r="J132" s="37" t="n"/>
+      <c r="K132" s="36" t="n"/>
     </row>
     <row r="133" ht="28" customHeight="1">
       <c r="A133" s="36" t="n"/>
@@ -20165,6 +20610,7 @@
       <c r="H133" s="39" t="n"/>
       <c r="I133" s="38" t="n"/>
       <c r="J133" s="37" t="n"/>
+      <c r="K133" s="36" t="n"/>
     </row>
     <row r="134" ht="28" customHeight="1">
       <c r="A134" s="36" t="n"/>
@@ -20177,6 +20623,7 @@
       <c r="H134" s="39" t="n"/>
       <c r="I134" s="38" t="n"/>
       <c r="J134" s="37" t="n"/>
+      <c r="K134" s="36" t="n"/>
     </row>
     <row r="135" ht="28" customHeight="1">
       <c r="A135" s="36" t="n"/>
@@ -20189,6 +20636,7 @@
       <c r="H135" s="39" t="n"/>
       <c r="I135" s="38" t="n"/>
       <c r="J135" s="37" t="n"/>
+      <c r="K135" s="36" t="n"/>
     </row>
     <row r="136" ht="28" customHeight="1">
       <c r="A136" s="36" t="n"/>
@@ -20201,6 +20649,7 @@
       <c r="H136" s="39" t="n"/>
       <c r="I136" s="38" t="n"/>
       <c r="J136" s="37" t="n"/>
+      <c r="K136" s="36" t="n"/>
     </row>
     <row r="137" ht="28" customHeight="1">
       <c r="A137" s="36" t="n"/>
@@ -20213,6 +20662,7 @@
       <c r="H137" s="39" t="n"/>
       <c r="I137" s="38" t="n"/>
       <c r="J137" s="37" t="n"/>
+      <c r="K137" s="36" t="n"/>
     </row>
     <row r="138" ht="28" customHeight="1">
       <c r="A138" s="36" t="n"/>
@@ -20225,6 +20675,7 @@
       <c r="H138" s="39" t="n"/>
       <c r="I138" s="38" t="n"/>
       <c r="J138" s="37" t="n"/>
+      <c r="K138" s="36" t="n"/>
     </row>
     <row r="139" ht="28" customHeight="1">
       <c r="A139" s="36" t="n"/>
@@ -20237,6 +20688,7 @@
       <c r="H139" s="39" t="n"/>
       <c r="I139" s="38" t="n"/>
       <c r="J139" s="37" t="n"/>
+      <c r="K139" s="36" t="n"/>
     </row>
     <row r="140" ht="28" customHeight="1">
       <c r="A140" s="36" t="n"/>
@@ -20249,6 +20701,7 @@
       <c r="H140" s="39" t="n"/>
       <c r="I140" s="38" t="n"/>
       <c r="J140" s="37" t="n"/>
+      <c r="K140" s="36" t="n"/>
     </row>
     <row r="141" ht="28" customHeight="1">
       <c r="A141" s="36" t="n"/>
@@ -20261,6 +20714,7 @@
       <c r="H141" s="39" t="n"/>
       <c r="I141" s="38" t="n"/>
       <c r="J141" s="37" t="n"/>
+      <c r="K141" s="36" t="n"/>
     </row>
     <row r="142" ht="28" customHeight="1">
       <c r="A142" s="36" t="n"/>
@@ -20273,6 +20727,7 @@
       <c r="H142" s="39" t="n"/>
       <c r="I142" s="38" t="n"/>
       <c r="J142" s="37" t="n"/>
+      <c r="K142" s="36" t="n"/>
     </row>
     <row r="143" ht="28" customHeight="1">
       <c r="A143" s="36" t="n"/>
@@ -20285,6 +20740,7 @@
       <c r="H143" s="39" t="n"/>
       <c r="I143" s="38" t="n"/>
       <c r="J143" s="37" t="n"/>
+      <c r="K143" s="36" t="n"/>
     </row>
     <row r="144" ht="28" customHeight="1">
       <c r="A144" s="36" t="n"/>
@@ -20297,6 +20753,7 @@
       <c r="H144" s="39" t="n"/>
       <c r="I144" s="38" t="n"/>
       <c r="J144" s="37" t="n"/>
+      <c r="K144" s="36" t="n"/>
     </row>
     <row r="145" ht="28" customHeight="1">
       <c r="A145" s="36" t="n"/>
@@ -20309,6 +20766,7 @@
       <c r="H145" s="39" t="n"/>
       <c r="I145" s="38" t="n"/>
       <c r="J145" s="37" t="n"/>
+      <c r="K145" s="36" t="n"/>
     </row>
     <row r="146" ht="28" customHeight="1">
       <c r="A146" s="36" t="n"/>
@@ -20321,6 +20779,7 @@
       <c r="H146" s="39" t="n"/>
       <c r="I146" s="38" t="n"/>
       <c r="J146" s="37" t="n"/>
+      <c r="K146" s="36" t="n"/>
     </row>
     <row r="147" ht="28" customHeight="1">
       <c r="A147" s="36" t="n"/>
@@ -20333,6 +20792,7 @@
       <c r="H147" s="39" t="n"/>
       <c r="I147" s="38" t="n"/>
       <c r="J147" s="37" t="n"/>
+      <c r="K147" s="36" t="n"/>
     </row>
     <row r="148" ht="28" customHeight="1">
       <c r="A148" s="36" t="n"/>
@@ -20345,6 +20805,7 @@
       <c r="H148" s="39" t="n"/>
       <c r="I148" s="38" t="n"/>
       <c r="J148" s="37" t="n"/>
+      <c r="K148" s="36" t="n"/>
     </row>
     <row r="149" ht="28" customHeight="1">
       <c r="A149" s="36" t="n"/>
@@ -20357,6 +20818,7 @@
       <c r="H149" s="39" t="n"/>
       <c r="I149" s="38" t="n"/>
       <c r="J149" s="37" t="n"/>
+      <c r="K149" s="36" t="n"/>
     </row>
     <row r="150" ht="28" customHeight="1">
       <c r="A150" s="36" t="n"/>
@@ -20369,6 +20831,7 @@
       <c r="H150" s="39" t="n"/>
       <c r="I150" s="38" t="n"/>
       <c r="J150" s="37" t="n"/>
+      <c r="K150" s="36" t="n"/>
     </row>
     <row r="151" ht="28" customHeight="1">
       <c r="A151" s="36" t="n"/>
@@ -20381,6 +20844,7 @@
       <c r="H151" s="39" t="n"/>
       <c r="I151" s="38" t="n"/>
       <c r="J151" s="37" t="n"/>
+      <c r="K151" s="36" t="n"/>
     </row>
     <row r="152" ht="28" customHeight="1">
       <c r="A152" s="36" t="n"/>
@@ -20393,6 +20857,7 @@
       <c r="H152" s="39" t="n"/>
       <c r="I152" s="38" t="n"/>
       <c r="J152" s="37" t="n"/>
+      <c r="K152" s="36" t="n"/>
     </row>
     <row r="153" ht="28" customHeight="1">
       <c r="A153" s="36" t="n"/>
@@ -20405,6 +20870,7 @@
       <c r="H153" s="39" t="n"/>
       <c r="I153" s="38" t="n"/>
       <c r="J153" s="37" t="n"/>
+      <c r="K153" s="36" t="n"/>
     </row>
     <row r="154" ht="28" customHeight="1">
       <c r="A154" s="36" t="n"/>
@@ -20417,6 +20883,7 @@
       <c r="H154" s="39" t="n"/>
       <c r="I154" s="38" t="n"/>
       <c r="J154" s="37" t="n"/>
+      <c r="K154" s="36" t="n"/>
     </row>
     <row r="155" ht="28" customHeight="1">
       <c r="A155" s="36" t="n"/>
@@ -20429,6 +20896,7 @@
       <c r="H155" s="39" t="n"/>
       <c r="I155" s="38" t="n"/>
       <c r="J155" s="37" t="n"/>
+      <c r="K155" s="36" t="n"/>
     </row>
     <row r="156" ht="28" customHeight="1">
       <c r="A156" s="36" t="n"/>
@@ -20441,6 +20909,7 @@
       <c r="H156" s="39" t="n"/>
       <c r="I156" s="38" t="n"/>
       <c r="J156" s="37" t="n"/>
+      <c r="K156" s="36" t="n"/>
     </row>
     <row r="157" ht="28" customHeight="1">
       <c r="A157" s="36" t="n"/>
@@ -20453,6 +20922,7 @@
       <c r="H157" s="39" t="n"/>
       <c r="I157" s="38" t="n"/>
       <c r="J157" s="37" t="n"/>
+      <c r="K157" s="36" t="n"/>
     </row>
     <row r="158" ht="28" customHeight="1">
       <c r="A158" s="36" t="n"/>
@@ -20465,6 +20935,7 @@
       <c r="H158" s="39" t="n"/>
       <c r="I158" s="38" t="n"/>
       <c r="J158" s="37" t="n"/>
+      <c r="K158" s="36" t="n"/>
     </row>
     <row r="159" ht="28" customHeight="1">
       <c r="A159" s="36" t="n"/>
@@ -20477,6 +20948,7 @@
       <c r="H159" s="39" t="n"/>
       <c r="I159" s="38" t="n"/>
       <c r="J159" s="37" t="n"/>
+      <c r="K159" s="36" t="n"/>
     </row>
     <row r="160" ht="28" customHeight="1">
       <c r="A160" s="36" t="n"/>
@@ -20489,6 +20961,7 @@
       <c r="H160" s="39" t="n"/>
       <c r="I160" s="38" t="n"/>
       <c r="J160" s="37" t="n"/>
+      <c r="K160" s="36" t="n"/>
     </row>
     <row r="161" ht="28" customHeight="1">
       <c r="A161" s="36" t="n"/>
@@ -20501,6 +20974,7 @@
       <c r="H161" s="39" t="n"/>
       <c r="I161" s="38" t="n"/>
       <c r="J161" s="37" t="n"/>
+      <c r="K161" s="36" t="n"/>
     </row>
     <row r="162" ht="28" customHeight="1">
       <c r="A162" s="36" t="n"/>
@@ -20513,6 +20987,7 @@
       <c r="H162" s="39" t="n"/>
       <c r="I162" s="38" t="n"/>
       <c r="J162" s="37" t="n"/>
+      <c r="K162" s="36" t="n"/>
     </row>
     <row r="163" ht="28" customHeight="1">
       <c r="A163" s="36" t="n"/>
@@ -20525,6 +21000,7 @@
       <c r="H163" s="39" t="n"/>
       <c r="I163" s="38" t="n"/>
       <c r="J163" s="37" t="n"/>
+      <c r="K163" s="36" t="n"/>
     </row>
     <row r="164" ht="28" customHeight="1">
       <c r="A164" s="36" t="n"/>
@@ -20537,6 +21013,7 @@
       <c r="H164" s="39" t="n"/>
       <c r="I164" s="38" t="n"/>
       <c r="J164" s="37" t="n"/>
+      <c r="K164" s="36" t="n"/>
     </row>
     <row r="165" ht="28" customHeight="1">
       <c r="A165" s="36" t="n"/>
@@ -20549,6 +21026,7 @@
       <c r="H165" s="39" t="n"/>
       <c r="I165" s="38" t="n"/>
       <c r="J165" s="37" t="n"/>
+      <c r="K165" s="36" t="n"/>
     </row>
     <row r="166" ht="28" customHeight="1">
       <c r="A166" s="36" t="n"/>
@@ -20561,6 +21039,7 @@
       <c r="H166" s="39" t="n"/>
       <c r="I166" s="38" t="n"/>
       <c r="J166" s="37" t="n"/>
+      <c r="K166" s="36" t="n"/>
     </row>
     <row r="167" ht="28" customHeight="1">
       <c r="A167" s="36" t="n"/>
@@ -20573,6 +21052,7 @@
       <c r="H167" s="39" t="n"/>
       <c r="I167" s="38" t="n"/>
       <c r="J167" s="37" t="n"/>
+      <c r="K167" s="36" t="n"/>
     </row>
     <row r="168" ht="28" customHeight="1">
       <c r="A168" s="36" t="n"/>
@@ -20585,6 +21065,7 @@
       <c r="H168" s="39" t="n"/>
       <c r="I168" s="38" t="n"/>
       <c r="J168" s="37" t="n"/>
+      <c r="K168" s="36" t="n"/>
     </row>
     <row r="169" ht="28" customHeight="1">
       <c r="A169" s="36" t="n"/>
@@ -20597,6 +21078,7 @@
       <c r="H169" s="39" t="n"/>
       <c r="I169" s="38" t="n"/>
       <c r="J169" s="37" t="n"/>
+      <c r="K169" s="36" t="n"/>
     </row>
     <row r="170" ht="28" customHeight="1">
       <c r="A170" s="36" t="n"/>
@@ -20609,6 +21091,7 @@
       <c r="H170" s="39" t="n"/>
       <c r="I170" s="38" t="n"/>
       <c r="J170" s="37" t="n"/>
+      <c r="K170" s="36" t="n"/>
     </row>
     <row r="171" ht="28" customHeight="1">
       <c r="A171" s="36" t="n"/>
@@ -20621,6 +21104,7 @@
       <c r="H171" s="39" t="n"/>
       <c r="I171" s="38" t="n"/>
       <c r="J171" s="37" t="n"/>
+      <c r="K171" s="36" t="n"/>
     </row>
     <row r="172" ht="28" customHeight="1">
       <c r="A172" s="36" t="n"/>
@@ -20633,6 +21117,7 @@
       <c r="H172" s="39" t="n"/>
       <c r="I172" s="38" t="n"/>
       <c r="J172" s="37" t="n"/>
+      <c r="K172" s="36" t="n"/>
     </row>
     <row r="173" ht="28" customHeight="1">
       <c r="A173" s="36" t="n"/>
@@ -20645,6 +21130,7 @@
       <c r="H173" s="39" t="n"/>
       <c r="I173" s="38" t="n"/>
       <c r="J173" s="37" t="n"/>
+      <c r="K173" s="36" t="n"/>
     </row>
     <row r="174" ht="28" customHeight="1">
       <c r="A174" s="36" t="n"/>
@@ -20657,6 +21143,7 @@
       <c r="H174" s="39" t="n"/>
       <c r="I174" s="38" t="n"/>
       <c r="J174" s="37" t="n"/>
+      <c r="K174" s="36" t="n"/>
     </row>
     <row r="175" ht="28" customHeight="1">
       <c r="A175" s="36" t="n"/>
@@ -20669,6 +21156,7 @@
       <c r="H175" s="39" t="n"/>
       <c r="I175" s="38" t="n"/>
       <c r="J175" s="37" t="n"/>
+      <c r="K175" s="36" t="n"/>
     </row>
     <row r="176" ht="28" customHeight="1">
       <c r="A176" s="36" t="n"/>
@@ -20681,6 +21169,7 @@
       <c r="H176" s="39" t="n"/>
       <c r="I176" s="38" t="n"/>
       <c r="J176" s="37" t="n"/>
+      <c r="K176" s="36" t="n"/>
     </row>
     <row r="177" ht="28" customHeight="1">
       <c r="A177" s="36" t="n"/>
@@ -20693,6 +21182,7 @@
       <c r="H177" s="39" t="n"/>
       <c r="I177" s="38" t="n"/>
       <c r="J177" s="37" t="n"/>
+      <c r="K177" s="36" t="n"/>
     </row>
     <row r="178" ht="28" customHeight="1">
       <c r="A178" s="36" t="n"/>
@@ -20705,6 +21195,7 @@
       <c r="H178" s="39" t="n"/>
       <c r="I178" s="38" t="n"/>
       <c r="J178" s="37" t="n"/>
+      <c r="K178" s="36" t="n"/>
     </row>
     <row r="179" ht="28" customHeight="1">
       <c r="A179" s="36" t="n"/>
@@ -20717,6 +21208,7 @@
       <c r="H179" s="39" t="n"/>
       <c r="I179" s="38" t="n"/>
       <c r="J179" s="37" t="n"/>
+      <c r="K179" s="36" t="n"/>
     </row>
     <row r="180" ht="28" customHeight="1">
       <c r="A180" s="36" t="n"/>
@@ -20729,6 +21221,7 @@
       <c r="H180" s="39" t="n"/>
       <c r="I180" s="38" t="n"/>
       <c r="J180" s="37" t="n"/>
+      <c r="K180" s="36" t="n"/>
     </row>
     <row r="181" ht="28" customHeight="1">
       <c r="A181" s="36" t="n"/>
@@ -20741,6 +21234,7 @@
       <c r="H181" s="39" t="n"/>
       <c r="I181" s="38" t="n"/>
       <c r="J181" s="37" t="n"/>
+      <c r="K181" s="36" t="n"/>
     </row>
     <row r="182" ht="28" customHeight="1">
       <c r="A182" s="36" t="n"/>
@@ -20753,6 +21247,7 @@
       <c r="H182" s="39" t="n"/>
       <c r="I182" s="38" t="n"/>
       <c r="J182" s="37" t="n"/>
+      <c r="K182" s="36" t="n"/>
     </row>
     <row r="183" ht="28" customHeight="1">
       <c r="A183" s="36" t="n"/>
@@ -20765,6 +21260,7 @@
       <c r="H183" s="39" t="n"/>
       <c r="I183" s="38" t="n"/>
       <c r="J183" s="37" t="n"/>
+      <c r="K183" s="36" t="n"/>
     </row>
     <row r="184" ht="28" customHeight="1">
       <c r="A184" s="36" t="n"/>
@@ -20777,6 +21273,7 @@
       <c r="H184" s="39" t="n"/>
       <c r="I184" s="38" t="n"/>
       <c r="J184" s="37" t="n"/>
+      <c r="K184" s="36" t="n"/>
     </row>
     <row r="185" ht="28" customHeight="1">
       <c r="A185" s="36" t="n"/>
@@ -20789,6 +21286,7 @@
       <c r="H185" s="39" t="n"/>
       <c r="I185" s="38" t="n"/>
       <c r="J185" s="37" t="n"/>
+      <c r="K185" s="36" t="n"/>
     </row>
     <row r="186" ht="28" customHeight="1">
       <c r="A186" s="36" t="n"/>
@@ -20801,6 +21299,7 @@
       <c r="H186" s="39" t="n"/>
       <c r="I186" s="38" t="n"/>
       <c r="J186" s="37" t="n"/>
+      <c r="K186" s="36" t="n"/>
     </row>
     <row r="187" ht="28" customHeight="1">
       <c r="A187" s="36" t="n"/>
@@ -20813,6 +21312,7 @@
       <c r="H187" s="39" t="n"/>
       <c r="I187" s="38" t="n"/>
       <c r="J187" s="37" t="n"/>
+      <c r="K187" s="36" t="n"/>
     </row>
     <row r="188" ht="28" customHeight="1">
       <c r="A188" s="36" t="n"/>
@@ -20825,6 +21325,7 @@
       <c r="H188" s="39" t="n"/>
       <c r="I188" s="38" t="n"/>
       <c r="J188" s="37" t="n"/>
+      <c r="K188" s="36" t="n"/>
     </row>
     <row r="189" ht="28" customHeight="1">
       <c r="A189" s="36" t="n"/>
@@ -20837,6 +21338,7 @@
       <c r="H189" s="39" t="n"/>
       <c r="I189" s="38" t="n"/>
       <c r="J189" s="37" t="n"/>
+      <c r="K189" s="36" t="n"/>
     </row>
     <row r="190" ht="28" customHeight="1">
       <c r="A190" s="36" t="n"/>
@@ -20849,6 +21351,7 @@
       <c r="H190" s="39" t="n"/>
       <c r="I190" s="38" t="n"/>
       <c r="J190" s="37" t="n"/>
+      <c r="K190" s="36" t="n"/>
     </row>
     <row r="191" ht="28" customHeight="1">
       <c r="A191" s="36" t="n"/>
@@ -20861,6 +21364,7 @@
       <c r="H191" s="39" t="n"/>
       <c r="I191" s="38" t="n"/>
       <c r="J191" s="37" t="n"/>
+      <c r="K191" s="36" t="n"/>
     </row>
     <row r="192" ht="28" customHeight="1">
       <c r="A192" s="36" t="n"/>
@@ -20873,6 +21377,7 @@
       <c r="H192" s="39" t="n"/>
       <c r="I192" s="38" t="n"/>
       <c r="J192" s="37" t="n"/>
+      <c r="K192" s="36" t="n"/>
     </row>
     <row r="193" ht="28" customHeight="1">
       <c r="A193" s="36" t="n"/>
@@ -20885,6 +21390,7 @@
       <c r="H193" s="39" t="n"/>
       <c r="I193" s="38" t="n"/>
       <c r="J193" s="37" t="n"/>
+      <c r="K193" s="36" t="n"/>
     </row>
     <row r="194" ht="28" customHeight="1">
       <c r="A194" s="36" t="n"/>
@@ -20897,6 +21403,7 @@
       <c r="H194" s="39" t="n"/>
       <c r="I194" s="38" t="n"/>
       <c r="J194" s="37" t="n"/>
+      <c r="K194" s="36" t="n"/>
     </row>
     <row r="195" ht="28" customHeight="1">
       <c r="A195" s="36" t="n"/>
@@ -20909,6 +21416,7 @@
       <c r="H195" s="39" t="n"/>
       <c r="I195" s="38" t="n"/>
       <c r="J195" s="37" t="n"/>
+      <c r="K195" s="36" t="n"/>
     </row>
     <row r="196" ht="28" customHeight="1">
       <c r="A196" s="36" t="n"/>
@@ -20921,6 +21429,7 @@
       <c r="H196" s="39" t="n"/>
       <c r="I196" s="38" t="n"/>
       <c r="J196" s="37" t="n"/>
+      <c r="K196" s="36" t="n"/>
     </row>
     <row r="197" ht="28" customHeight="1">
       <c r="A197" s="36" t="n"/>
@@ -20933,6 +21442,7 @@
       <c r="H197" s="39" t="n"/>
       <c r="I197" s="38" t="n"/>
       <c r="J197" s="37" t="n"/>
+      <c r="K197" s="36" t="n"/>
     </row>
     <row r="198" ht="28" customHeight="1">
       <c r="A198" s="36" t="n"/>
@@ -20945,6 +21455,7 @@
       <c r="H198" s="39" t="n"/>
       <c r="I198" s="38" t="n"/>
       <c r="J198" s="37" t="n"/>
+      <c r="K198" s="36" t="n"/>
     </row>
     <row r="199" ht="28" customHeight="1">
       <c r="A199" s="36" t="n"/>
@@ -20957,6 +21468,7 @@
       <c r="H199" s="39" t="n"/>
       <c r="I199" s="38" t="n"/>
       <c r="J199" s="37" t="n"/>
+      <c r="K199" s="36" t="n"/>
     </row>
     <row r="200" ht="28" customHeight="1">
       <c r="A200" s="36" t="n"/>
@@ -20969,6 +21481,7 @@
       <c r="H200" s="39" t="n"/>
       <c r="I200" s="38" t="n"/>
       <c r="J200" s="37" t="n"/>
+      <c r="K200" s="36" t="n"/>
     </row>
     <row r="201" ht="28" customHeight="1">
       <c r="A201" s="36" t="n"/>
@@ -20981,6 +21494,7 @@
       <c r="H201" s="39" t="n"/>
       <c r="I201" s="38" t="n"/>
       <c r="J201" s="37" t="n"/>
+      <c r="K201" s="36" t="n"/>
     </row>
     <row r="202" ht="28" customHeight="1">
       <c r="A202" s="36" t="n"/>
@@ -20993,6 +21507,7 @@
       <c r="H202" s="39" t="n"/>
       <c r="I202" s="38" t="n"/>
       <c r="J202" s="37" t="n"/>
+      <c r="K202" s="36" t="n"/>
     </row>
     <row r="203" ht="28" customHeight="1">
       <c r="A203" s="36" t="n"/>
@@ -21005,6 +21520,7 @@
       <c r="H203" s="39" t="n"/>
       <c r="I203" s="38" t="n"/>
       <c r="J203" s="37" t="n"/>
+      <c r="K203" s="36" t="n"/>
     </row>
     <row r="204" ht="28" customHeight="1">
       <c r="A204" s="36" t="n"/>
@@ -21017,6 +21533,7 @@
       <c r="H204" s="39" t="n"/>
       <c r="I204" s="38" t="n"/>
       <c r="J204" s="37" t="n"/>
+      <c r="K204" s="36" t="n"/>
     </row>
     <row r="205" ht="28" customHeight="1">
       <c r="A205" s="36" t="n"/>
@@ -21029,6 +21546,7 @@
       <c r="H205" s="39" t="n"/>
       <c r="I205" s="38" t="n"/>
       <c r="J205" s="37" t="n"/>
+      <c r="K205" s="36" t="n"/>
     </row>
     <row r="206" ht="28" customHeight="1">
       <c r="A206" s="36" t="n"/>
@@ -21041,6 +21559,7 @@
       <c r="H206" s="39" t="n"/>
       <c r="I206" s="38" t="n"/>
       <c r="J206" s="37" t="n"/>
+      <c r="K206" s="36" t="n"/>
     </row>
     <row r="207" ht="28" customHeight="1">
       <c r="A207" s="36" t="n"/>
@@ -21053,6 +21572,7 @@
       <c r="H207" s="39" t="n"/>
       <c r="I207" s="38" t="n"/>
       <c r="J207" s="37" t="n"/>
+      <c r="K207" s="36" t="n"/>
     </row>
     <row r="208" ht="28" customHeight="1">
       <c r="A208" s="36" t="n"/>
@@ -21065,6 +21585,7 @@
       <c r="H208" s="39" t="n"/>
       <c r="I208" s="38" t="n"/>
       <c r="J208" s="37" t="n"/>
+      <c r="K208" s="36" t="n"/>
     </row>
     <row r="209" ht="28" customHeight="1">
       <c r="A209" s="36" t="n"/>
@@ -21077,6 +21598,7 @@
       <c r="H209" s="39" t="n"/>
       <c r="I209" s="38" t="n"/>
       <c r="J209" s="37" t="n"/>
+      <c r="K209" s="36" t="n"/>
     </row>
     <row r="210" ht="28" customHeight="1">
       <c r="A210" s="36" t="n"/>
@@ -21089,6 +21611,7 @@
       <c r="H210" s="39" t="n"/>
       <c r="I210" s="38" t="n"/>
       <c r="J210" s="37" t="n"/>
+      <c r="K210" s="36" t="n"/>
     </row>
     <row r="211" ht="28" customHeight="1">
       <c r="A211" s="36" t="n"/>
@@ -21101,6 +21624,7 @@
       <c r="H211" s="39" t="n"/>
       <c r="I211" s="38" t="n"/>
       <c r="J211" s="37" t="n"/>
+      <c r="K211" s="36" t="n"/>
     </row>
     <row r="212" ht="28" customHeight="1">
       <c r="A212" s="36" t="n"/>
@@ -21113,6 +21637,7 @@
       <c r="H212" s="39" t="n"/>
       <c r="I212" s="38" t="n"/>
       <c r="J212" s="37" t="n"/>
+      <c r="K212" s="36" t="n"/>
     </row>
     <row r="213" ht="28" customHeight="1">
       <c r="A213" s="36" t="n"/>
@@ -21125,6 +21650,7 @@
       <c r="H213" s="39" t="n"/>
       <c r="I213" s="38" t="n"/>
       <c r="J213" s="37" t="n"/>
+      <c r="K213" s="36" t="n"/>
     </row>
     <row r="214" ht="28" customHeight="1">
       <c r="A214" s="36" t="n"/>
@@ -21137,6 +21663,7 @@
       <c r="H214" s="39" t="n"/>
       <c r="I214" s="38" t="n"/>
       <c r="J214" s="37" t="n"/>
+      <c r="K214" s="36" t="n"/>
     </row>
     <row r="215" ht="28" customHeight="1">
       <c r="A215" s="36" t="n"/>
@@ -21149,6 +21676,7 @@
       <c r="H215" s="39" t="n"/>
       <c r="I215" s="38" t="n"/>
       <c r="J215" s="37" t="n"/>
+      <c r="K215" s="36" t="n"/>
     </row>
     <row r="216" ht="28" customHeight="1">
       <c r="A216" s="36" t="n"/>
@@ -21161,6 +21689,7 @@
       <c r="H216" s="39" t="n"/>
       <c r="I216" s="38" t="n"/>
       <c r="J216" s="37" t="n"/>
+      <c r="K216" s="36" t="n"/>
     </row>
     <row r="217" ht="28" customHeight="1">
       <c r="A217" s="36" t="n"/>
@@ -21173,6 +21702,7 @@
       <c r="H217" s="39" t="n"/>
       <c r="I217" s="38" t="n"/>
       <c r="J217" s="37" t="n"/>
+      <c r="K217" s="36" t="n"/>
     </row>
     <row r="218" ht="28" customHeight="1">
       <c r="A218" s="36" t="n"/>
@@ -21185,6 +21715,7 @@
       <c r="H218" s="39" t="n"/>
       <c r="I218" s="38" t="n"/>
       <c r="J218" s="37" t="n"/>
+      <c r="K218" s="36" t="n"/>
     </row>
     <row r="219" ht="28" customHeight="1">
       <c r="A219" s="36" t="n"/>
@@ -21197,6 +21728,7 @@
       <c r="H219" s="39" t="n"/>
       <c r="I219" s="38" t="n"/>
       <c r="J219" s="37" t="n"/>
+      <c r="K219" s="36" t="n"/>
     </row>
     <row r="220" ht="28" customHeight="1">
       <c r="A220" s="36" t="n"/>
@@ -21209,6 +21741,7 @@
       <c r="H220" s="39" t="n"/>
       <c r="I220" s="38" t="n"/>
       <c r="J220" s="37" t="n"/>
+      <c r="K220" s="36" t="n"/>
     </row>
     <row r="221" ht="28" customHeight="1">
       <c r="A221" s="36" t="n"/>
@@ -21221,6 +21754,7 @@
       <c r="H221" s="39" t="n"/>
       <c r="I221" s="38" t="n"/>
       <c r="J221" s="37" t="n"/>
+      <c r="K221" s="36" t="n"/>
     </row>
     <row r="222" ht="28" customHeight="1">
       <c r="A222" s="36" t="n"/>
@@ -21233,6 +21767,7 @@
       <c r="H222" s="39" t="n"/>
       <c r="I222" s="38" t="n"/>
       <c r="J222" s="37" t="n"/>
+      <c r="K222" s="36" t="n"/>
     </row>
     <row r="223" ht="28" customHeight="1">
       <c r="A223" s="36" t="n"/>
@@ -21245,6 +21780,7 @@
       <c r="H223" s="39" t="n"/>
       <c r="I223" s="38" t="n"/>
       <c r="J223" s="37" t="n"/>
+      <c r="K223" s="36" t="n"/>
     </row>
     <row r="224" ht="28" customHeight="1">
       <c r="A224" s="36" t="n"/>
@@ -21257,6 +21793,7 @@
       <c r="H224" s="39" t="n"/>
       <c r="I224" s="38" t="n"/>
       <c r="J224" s="37" t="n"/>
+      <c r="K224" s="36" t="n"/>
     </row>
     <row r="225" ht="28" customHeight="1">
       <c r="A225" s="36" t="n"/>
@@ -21269,6 +21806,7 @@
       <c r="H225" s="39" t="n"/>
       <c r="I225" s="38" t="n"/>
       <c r="J225" s="37" t="n"/>
+      <c r="K225" s="36" t="n"/>
     </row>
     <row r="226" ht="28" customHeight="1">
       <c r="A226" s="36" t="n"/>
@@ -21281,6 +21819,7 @@
       <c r="H226" s="39" t="n"/>
       <c r="I226" s="38" t="n"/>
       <c r="J226" s="37" t="n"/>
+      <c r="K226" s="36" t="n"/>
     </row>
     <row r="227" ht="28" customHeight="1">
       <c r="A227" s="36" t="n"/>
@@ -21293,6 +21832,7 @@
       <c r="H227" s="39" t="n"/>
       <c r="I227" s="38" t="n"/>
       <c r="J227" s="37" t="n"/>
+      <c r="K227" s="36" t="n"/>
     </row>
     <row r="228" ht="28" customHeight="1">
       <c r="A228" s="36" t="n"/>
@@ -21305,6 +21845,7 @@
       <c r="H228" s="39" t="n"/>
       <c r="I228" s="38" t="n"/>
       <c r="J228" s="37" t="n"/>
+      <c r="K228" s="36" t="n"/>
     </row>
     <row r="229" ht="28" customHeight="1">
       <c r="A229" s="36" t="n"/>
@@ -21317,6 +21858,7 @@
       <c r="H229" s="39" t="n"/>
       <c r="I229" s="38" t="n"/>
       <c r="J229" s="37" t="n"/>
+      <c r="K229" s="36" t="n"/>
     </row>
     <row r="230" ht="28" customHeight="1">
       <c r="A230" s="36" t="n"/>
@@ -21329,6 +21871,7 @@
       <c r="H230" s="39" t="n"/>
       <c r="I230" s="38" t="n"/>
       <c r="J230" s="37" t="n"/>
+      <c r="K230" s="36" t="n"/>
     </row>
     <row r="231" ht="28" customHeight="1">
       <c r="A231" s="36" t="n"/>
@@ -21341,6 +21884,7 @@
       <c r="H231" s="39" t="n"/>
       <c r="I231" s="38" t="n"/>
       <c r="J231" s="37" t="n"/>
+      <c r="K231" s="36" t="n"/>
     </row>
     <row r="232" ht="28" customHeight="1">
       <c r="A232" s="36" t="n"/>
@@ -21353,6 +21897,7 @@
       <c r="H232" s="39" t="n"/>
       <c r="I232" s="38" t="n"/>
       <c r="J232" s="37" t="n"/>
+      <c r="K232" s="36" t="n"/>
     </row>
     <row r="233" ht="28" customHeight="1">
       <c r="A233" s="36" t="n"/>
@@ -21365,6 +21910,7 @@
       <c r="H233" s="39" t="n"/>
       <c r="I233" s="38" t="n"/>
       <c r="J233" s="37" t="n"/>
+      <c r="K233" s="36" t="n"/>
     </row>
     <row r="234" ht="28" customHeight="1">
       <c r="A234" s="36" t="n"/>
@@ -21377,6 +21923,7 @@
       <c r="H234" s="39" t="n"/>
       <c r="I234" s="38" t="n"/>
       <c r="J234" s="37" t="n"/>
+      <c r="K234" s="36" t="n"/>
     </row>
     <row r="235" ht="28" customHeight="1">
       <c r="A235" s="36" t="n"/>
@@ -21389,6 +21936,7 @@
       <c r="H235" s="39" t="n"/>
       <c r="I235" s="38" t="n"/>
       <c r="J235" s="37" t="n"/>
+      <c r="K235" s="36" t="n"/>
     </row>
     <row r="236" ht="28" customHeight="1">
       <c r="A236" s="36" t="n"/>
@@ -21401,6 +21949,7 @@
       <c r="H236" s="39" t="n"/>
       <c r="I236" s="38" t="n"/>
       <c r="J236" s="37" t="n"/>
+      <c r="K236" s="36" t="n"/>
     </row>
     <row r="237" ht="28" customHeight="1">
       <c r="A237" s="36" t="n"/>
@@ -21413,6 +21962,7 @@
       <c r="H237" s="39" t="n"/>
       <c r="I237" s="38" t="n"/>
       <c r="J237" s="37" t="n"/>
+      <c r="K237" s="36" t="n"/>
     </row>
     <row r="238" ht="28" customHeight="1">
       <c r="A238" s="36" t="n"/>
@@ -21425,6 +21975,7 @@
       <c r="H238" s="39" t="n"/>
       <c r="I238" s="38" t="n"/>
       <c r="J238" s="37" t="n"/>
+      <c r="K238" s="36" t="n"/>
     </row>
     <row r="239" ht="28" customHeight="1">
       <c r="A239" s="36" t="n"/>
@@ -21437,6 +21988,7 @@
       <c r="H239" s="39" t="n"/>
       <c r="I239" s="38" t="n"/>
       <c r="J239" s="37" t="n"/>
+      <c r="K239" s="36" t="n"/>
     </row>
     <row r="240" ht="28" customHeight="1">
       <c r="A240" s="36" t="n"/>
@@ -21449,6 +22001,7 @@
       <c r="H240" s="39" t="n"/>
       <c r="I240" s="38" t="n"/>
       <c r="J240" s="37" t="n"/>
+      <c r="K240" s="36" t="n"/>
     </row>
     <row r="241" ht="28" customHeight="1">
       <c r="A241" s="36" t="n"/>
@@ -21461,6 +22014,7 @@
       <c r="H241" s="39" t="n"/>
       <c r="I241" s="38" t="n"/>
       <c r="J241" s="37" t="n"/>
+      <c r="K241" s="36" t="n"/>
     </row>
     <row r="242" ht="28" customHeight="1">
       <c r="A242" s="36" t="n"/>
@@ -21473,6 +22027,7 @@
       <c r="H242" s="39" t="n"/>
       <c r="I242" s="38" t="n"/>
       <c r="J242" s="37" t="n"/>
+      <c r="K242" s="36" t="n"/>
     </row>
     <row r="243" ht="28" customHeight="1">
       <c r="A243" s="36" t="n"/>
@@ -21485,6 +22040,7 @@
       <c r="H243" s="39" t="n"/>
       <c r="I243" s="38" t="n"/>
       <c r="J243" s="37" t="n"/>
+      <c r="K243" s="36" t="n"/>
     </row>
     <row r="244" ht="28" customHeight="1">
       <c r="A244" s="36" t="n"/>
@@ -21497,6 +22053,7 @@
       <c r="H244" s="39" t="n"/>
       <c r="I244" s="38" t="n"/>
       <c r="J244" s="37" t="n"/>
+      <c r="K244" s="36" t="n"/>
     </row>
     <row r="245" ht="28" customHeight="1">
       <c r="A245" s="36" t="n"/>
@@ -21509,6 +22066,7 @@
       <c r="H245" s="39" t="n"/>
       <c r="I245" s="38" t="n"/>
       <c r="J245" s="37" t="n"/>
+      <c r="K245" s="36" t="n"/>
     </row>
     <row r="246" ht="28" customHeight="1">
       <c r="A246" s="36" t="n"/>
@@ -21521,6 +22079,7 @@
       <c r="H246" s="39" t="n"/>
       <c r="I246" s="38" t="n"/>
       <c r="J246" s="37" t="n"/>
+      <c r="K246" s="36" t="n"/>
     </row>
     <row r="247" ht="28" customHeight="1">
       <c r="A247" s="36" t="n"/>
@@ -21533,6 +22092,7 @@
       <c r="H247" s="39" t="n"/>
       <c r="I247" s="38" t="n"/>
       <c r="J247" s="37" t="n"/>
+      <c r="K247" s="36" t="n"/>
     </row>
     <row r="248" ht="28" customHeight="1">
       <c r="A248" s="36" t="n"/>
@@ -21545,6 +22105,7 @@
       <c r="H248" s="39" t="n"/>
       <c r="I248" s="38" t="n"/>
       <c r="J248" s="37" t="n"/>
+      <c r="K248" s="36" t="n"/>
     </row>
     <row r="249" ht="28" customHeight="1">
       <c r="A249" s="36" t="n"/>
@@ -21557,6 +22118,7 @@
       <c r="H249" s="39" t="n"/>
       <c r="I249" s="38" t="n"/>
       <c r="J249" s="37" t="n"/>
+      <c r="K249" s="36" t="n"/>
     </row>
     <row r="250" ht="28" customHeight="1">
       <c r="A250" s="36" t="n"/>
@@ -21569,6 +22131,7 @@
       <c r="H250" s="39" t="n"/>
       <c r="I250" s="38" t="n"/>
       <c r="J250" s="37" t="n"/>
+      <c r="K250" s="36" t="n"/>
     </row>
     <row r="251" ht="28" customHeight="1">
       <c r="A251" s="36" t="n"/>
@@ -21581,6 +22144,7 @@
       <c r="H251" s="39" t="n"/>
       <c r="I251" s="38" t="n"/>
       <c r="J251" s="37" t="n"/>
+      <c r="K251" s="36" t="n"/>
     </row>
     <row r="252" ht="28" customHeight="1">
       <c r="A252" s="36" t="n"/>
@@ -21593,6 +22157,7 @@
       <c r="H252" s="39" t="n"/>
       <c r="I252" s="38" t="n"/>
       <c r="J252" s="37" t="n"/>
+      <c r="K252" s="36" t="n"/>
     </row>
     <row r="253" ht="28" customHeight="1">
       <c r="A253" s="36" t="n"/>
@@ -21605,6 +22170,7 @@
       <c r="H253" s="39" t="n"/>
       <c r="I253" s="38" t="n"/>
       <c r="J253" s="37" t="n"/>
+      <c r="K253" s="36" t="n"/>
     </row>
     <row r="254" ht="28" customHeight="1">
       <c r="A254" s="36" t="n"/>
@@ -21617,6 +22183,7 @@
       <c r="H254" s="39" t="n"/>
       <c r="I254" s="38" t="n"/>
       <c r="J254" s="37" t="n"/>
+      <c r="K254" s="36" t="n"/>
     </row>
     <row r="255" ht="28" customHeight="1">
       <c r="A255" s="36" t="n"/>
@@ -21629,6 +22196,7 @@
       <c r="H255" s="39" t="n"/>
       <c r="I255" s="38" t="n"/>
       <c r="J255" s="37" t="n"/>
+      <c r="K255" s="36" t="n"/>
     </row>
     <row r="256" ht="28" customHeight="1">
       <c r="A256" s="36" t="n"/>
@@ -21641,6 +22209,7 @@
       <c r="H256" s="39" t="n"/>
       <c r="I256" s="38" t="n"/>
       <c r="J256" s="37" t="n"/>
+      <c r="K256" s="36" t="n"/>
     </row>
     <row r="257" ht="28" customHeight="1">
       <c r="A257" s="36" t="n"/>
@@ -21653,6 +22222,7 @@
       <c r="H257" s="39" t="n"/>
       <c r="I257" s="38" t="n"/>
       <c r="J257" s="37" t="n"/>
+      <c r="K257" s="36" t="n"/>
     </row>
     <row r="258" ht="28" customHeight="1">
       <c r="A258" s="36" t="n"/>
@@ -21665,6 +22235,7 @@
       <c r="H258" s="39" t="n"/>
       <c r="I258" s="38" t="n"/>
       <c r="J258" s="37" t="n"/>
+      <c r="K258" s="36" t="n"/>
     </row>
     <row r="259" ht="28" customHeight="1">
       <c r="A259" s="36" t="n"/>
@@ -21677,6 +22248,7 @@
       <c r="H259" s="39" t="n"/>
       <c r="I259" s="38" t="n"/>
       <c r="J259" s="37" t="n"/>
+      <c r="K259" s="36" t="n"/>
     </row>
     <row r="260" ht="28" customHeight="1">
       <c r="A260" s="36" t="n"/>
@@ -21689,6 +22261,7 @@
       <c r="H260" s="39" t="n"/>
       <c r="I260" s="38" t="n"/>
       <c r="J260" s="37" t="n"/>
+      <c r="K260" s="36" t="n"/>
     </row>
     <row r="261" ht="28" customHeight="1">
       <c r="A261" s="36" t="n"/>
@@ -21701,6 +22274,7 @@
       <c r="H261" s="39" t="n"/>
       <c r="I261" s="38" t="n"/>
       <c r="J261" s="37" t="n"/>
+      <c r="K261" s="36" t="n"/>
     </row>
     <row r="262" ht="28" customHeight="1">
       <c r="A262" s="36" t="n"/>
@@ -21713,6 +22287,7 @@
       <c r="H262" s="39" t="n"/>
       <c r="I262" s="38" t="n"/>
       <c r="J262" s="37" t="n"/>
+      <c r="K262" s="36" t="n"/>
     </row>
     <row r="263" ht="28" customHeight="1">
       <c r="A263" s="36" t="n"/>
@@ -21725,6 +22300,7 @@
       <c r="H263" s="39" t="n"/>
       <c r="I263" s="38" t="n"/>
       <c r="J263" s="37" t="n"/>
+      <c r="K263" s="36" t="n"/>
     </row>
     <row r="264" ht="28" customHeight="1">
       <c r="A264" s="36" t="n"/>
@@ -21737,6 +22313,7 @@
       <c r="H264" s="39" t="n"/>
       <c r="I264" s="38" t="n"/>
       <c r="J264" s="37" t="n"/>
+      <c r="K264" s="36" t="n"/>
     </row>
     <row r="265" ht="28" customHeight="1">
       <c r="A265" s="36" t="n"/>
@@ -21749,6 +22326,7 @@
       <c r="H265" s="39" t="n"/>
       <c r="I265" s="38" t="n"/>
       <c r="J265" s="37" t="n"/>
+      <c r="K265" s="36" t="n"/>
     </row>
     <row r="266" ht="28" customHeight="1">
       <c r="A266" s="36" t="n"/>
@@ -21761,6 +22339,7 @@
       <c r="H266" s="39" t="n"/>
       <c r="I266" s="38" t="n"/>
       <c r="J266" s="37" t="n"/>
+      <c r="K266" s="36" t="n"/>
     </row>
     <row r="267" ht="28" customHeight="1">
       <c r="A267" s="36" t="n"/>
@@ -21773,6 +22352,7 @@
       <c r="H267" s="39" t="n"/>
       <c r="I267" s="38" t="n"/>
       <c r="J267" s="37" t="n"/>
+      <c r="K267" s="36" t="n"/>
     </row>
     <row r="268" ht="28" customHeight="1">
       <c r="A268" s="36" t="n"/>
@@ -21785,6 +22365,7 @@
       <c r="H268" s="39" t="n"/>
       <c r="I268" s="38" t="n"/>
       <c r="J268" s="37" t="n"/>
+      <c r="K268" s="36" t="n"/>
     </row>
     <row r="269" ht="28" customHeight="1">
       <c r="A269" s="36" t="n"/>
@@ -21797,6 +22378,7 @@
       <c r="H269" s="39" t="n"/>
       <c r="I269" s="38" t="n"/>
       <c r="J269" s="37" t="n"/>
+      <c r="K269" s="36" t="n"/>
     </row>
     <row r="270" ht="28" customHeight="1">
       <c r="A270" s="36" t="n"/>
@@ -21809,6 +22391,7 @@
       <c r="H270" s="39" t="n"/>
       <c r="I270" s="38" t="n"/>
       <c r="J270" s="37" t="n"/>
+      <c r="K270" s="36" t="n"/>
     </row>
     <row r="271" ht="28" customHeight="1">
       <c r="A271" s="36" t="n"/>
@@ -21821,6 +22404,7 @@
       <c r="H271" s="39" t="n"/>
       <c r="I271" s="38" t="n"/>
       <c r="J271" s="37" t="n"/>
+      <c r="K271" s="36" t="n"/>
     </row>
     <row r="272" ht="28" customHeight="1">
       <c r="A272" s="36" t="n"/>
@@ -21833,6 +22417,7 @@
       <c r="H272" s="39" t="n"/>
       <c r="I272" s="38" t="n"/>
       <c r="J272" s="37" t="n"/>
+      <c r="K272" s="36" t="n"/>
     </row>
     <row r="273" ht="28" customHeight="1">
       <c r="A273" s="36" t="n"/>
@@ -21845,6 +22430,7 @@
       <c r="H273" s="39" t="n"/>
       <c r="I273" s="38" t="n"/>
       <c r="J273" s="37" t="n"/>
+      <c r="K273" s="36" t="n"/>
     </row>
     <row r="274" ht="28" customHeight="1">
       <c r="A274" s="36" t="n"/>
@@ -21857,6 +22443,7 @@
       <c r="H274" s="39" t="n"/>
       <c r="I274" s="38" t="n"/>
       <c r="J274" s="37" t="n"/>
+      <c r="K274" s="36" t="n"/>
     </row>
     <row r="275" ht="28" customHeight="1">
       <c r="A275" s="36" t="n"/>
@@ -21869,6 +22456,7 @@
       <c r="H275" s="39" t="n"/>
       <c r="I275" s="38" t="n"/>
       <c r="J275" s="37" t="n"/>
+      <c r="K275" s="36" t="n"/>
     </row>
     <row r="276" ht="28" customHeight="1">
       <c r="A276" s="36" t="n"/>
@@ -21881,6 +22469,7 @@
       <c r="H276" s="39" t="n"/>
       <c r="I276" s="38" t="n"/>
       <c r="J276" s="37" t="n"/>
+      <c r="K276" s="36" t="n"/>
     </row>
     <row r="277" ht="28" customHeight="1">
       <c r="A277" s="36" t="n"/>
@@ -21893,6 +22482,7 @@
       <c r="H277" s="39" t="n"/>
       <c r="I277" s="38" t="n"/>
       <c r="J277" s="37" t="n"/>
+      <c r="K277" s="36" t="n"/>
     </row>
     <row r="278" ht="28" customHeight="1">
       <c r="A278" s="36" t="n"/>
@@ -21905,6 +22495,7 @@
       <c r="H278" s="39" t="n"/>
       <c r="I278" s="38" t="n"/>
       <c r="J278" s="37" t="n"/>
+      <c r="K278" s="36" t="n"/>
     </row>
     <row r="279" ht="28" customHeight="1">
       <c r="A279" s="36" t="n"/>
@@ -21917,6 +22508,7 @@
       <c r="H279" s="39" t="n"/>
       <c r="I279" s="38" t="n"/>
       <c r="J279" s="37" t="n"/>
+      <c r="K279" s="36" t="n"/>
     </row>
     <row r="280" ht="28" customHeight="1">
       <c r="A280" s="36" t="n"/>
@@ -21929,6 +22521,7 @@
       <c r="H280" s="39" t="n"/>
       <c r="I280" s="38" t="n"/>
       <c r="J280" s="37" t="n"/>
+      <c r="K280" s="36" t="n"/>
     </row>
     <row r="281" ht="28" customHeight="1">
       <c r="A281" s="36" t="n"/>
@@ -21941,6 +22534,7 @@
       <c r="H281" s="39" t="n"/>
       <c r="I281" s="38" t="n"/>
       <c r="J281" s="37" t="n"/>
+      <c r="K281" s="36" t="n"/>
     </row>
     <row r="282" ht="28" customHeight="1">
       <c r="A282" s="36" t="n"/>
@@ -21953,6 +22547,7 @@
       <c r="H282" s="39" t="n"/>
       <c r="I282" s="38" t="n"/>
       <c r="J282" s="37" t="n"/>
+      <c r="K282" s="36" t="n"/>
     </row>
     <row r="283" ht="28" customHeight="1">
       <c r="A283" s="36" t="n"/>
@@ -21965,6 +22560,7 @@
       <c r="H283" s="39" t="n"/>
       <c r="I283" s="38" t="n"/>
       <c r="J283" s="37" t="n"/>
+      <c r="K283" s="36" t="n"/>
     </row>
     <row r="284" ht="28" customHeight="1">
       <c r="A284" s="36" t="n"/>
@@ -21977,6 +22573,7 @@
       <c r="H284" s="39" t="n"/>
       <c r="I284" s="38" t="n"/>
       <c r="J284" s="37" t="n"/>
+      <c r="K284" s="36" t="n"/>
     </row>
     <row r="285" ht="28" customHeight="1">
       <c r="A285" s="36" t="n"/>
@@ -21989,6 +22586,7 @@
       <c r="H285" s="39" t="n"/>
       <c r="I285" s="38" t="n"/>
       <c r="J285" s="37" t="n"/>
+      <c r="K285" s="36" t="n"/>
     </row>
     <row r="286" ht="28" customHeight="1">
       <c r="A286" s="36" t="n"/>
@@ -22001,6 +22599,7 @@
       <c r="H286" s="39" t="n"/>
       <c r="I286" s="38" t="n"/>
       <c r="J286" s="37" t="n"/>
+      <c r="K286" s="36" t="n"/>
     </row>
     <row r="287" ht="28" customHeight="1">
       <c r="A287" s="36" t="n"/>
@@ -22013,6 +22612,7 @@
       <c r="H287" s="39" t="n"/>
       <c r="I287" s="38" t="n"/>
       <c r="J287" s="37" t="n"/>
+      <c r="K287" s="36" t="n"/>
     </row>
     <row r="288" ht="28" customHeight="1">
       <c r="A288" s="36" t="n"/>
@@ -22025,6 +22625,7 @@
       <c r="H288" s="39" t="n"/>
       <c r="I288" s="38" t="n"/>
       <c r="J288" s="37" t="n"/>
+      <c r="K288" s="36" t="n"/>
     </row>
     <row r="289" ht="28" customHeight="1">
       <c r="A289" s="36" t="n"/>
@@ -22037,6 +22638,7 @@
       <c r="H289" s="39" t="n"/>
       <c r="I289" s="38" t="n"/>
       <c r="J289" s="37" t="n"/>
+      <c r="K289" s="36" t="n"/>
     </row>
     <row r="290" ht="28" customHeight="1">
       <c r="A290" s="36" t="n"/>
@@ -22049,6 +22651,7 @@
       <c r="H290" s="39" t="n"/>
       <c r="I290" s="38" t="n"/>
       <c r="J290" s="37" t="n"/>
+      <c r="K290" s="36" t="n"/>
     </row>
     <row r="291" ht="28" customHeight="1">
       <c r="A291" s="36" t="n"/>
@@ -22061,6 +22664,7 @@
       <c r="H291" s="39" t="n"/>
       <c r="I291" s="38" t="n"/>
       <c r="J291" s="37" t="n"/>
+      <c r="K291" s="36" t="n"/>
     </row>
     <row r="292" ht="28" customHeight="1">
       <c r="A292" s="36" t="n"/>
@@ -22073,6 +22677,7 @@
       <c r="H292" s="39" t="n"/>
       <c r="I292" s="38" t="n"/>
       <c r="J292" s="37" t="n"/>
+      <c r="K292" s="36" t="n"/>
     </row>
     <row r="293" ht="28" customHeight="1">
       <c r="A293" s="36" t="n"/>
@@ -22085,6 +22690,7 @@
       <c r="H293" s="39" t="n"/>
       <c r="I293" s="38" t="n"/>
       <c r="J293" s="37" t="n"/>
+      <c r="K293" s="36" t="n"/>
     </row>
     <row r="294" ht="28" customHeight="1">
       <c r="A294" s="36" t="n"/>
@@ -22097,6 +22703,7 @@
       <c r="H294" s="39" t="n"/>
       <c r="I294" s="38" t="n"/>
       <c r="J294" s="37" t="n"/>
+      <c r="K294" s="36" t="n"/>
     </row>
     <row r="295" ht="28" customHeight="1">
       <c r="A295" s="36" t="n"/>
@@ -22109,6 +22716,7 @@
       <c r="H295" s="39" t="n"/>
       <c r="I295" s="38" t="n"/>
       <c r="J295" s="37" t="n"/>
+      <c r="K295" s="36" t="n"/>
     </row>
     <row r="296" ht="28" customHeight="1">
       <c r="A296" s="36" t="n"/>
@@ -22121,6 +22729,7 @@
       <c r="H296" s="39" t="n"/>
       <c r="I296" s="38" t="n"/>
       <c r="J296" s="37" t="n"/>
+      <c r="K296" s="36" t="n"/>
     </row>
     <row r="297" ht="28" customHeight="1">
       <c r="A297" s="36" t="n"/>
@@ -22133,6 +22742,7 @@
       <c r="H297" s="39" t="n"/>
       <c r="I297" s="38" t="n"/>
       <c r="J297" s="37" t="n"/>
+      <c r="K297" s="36" t="n"/>
     </row>
     <row r="298" ht="28" customHeight="1">
       <c r="A298" s="36" t="n"/>
@@ -22145,6 +22755,7 @@
       <c r="H298" s="39" t="n"/>
       <c r="I298" s="38" t="n"/>
       <c r="J298" s="37" t="n"/>
+      <c r="K298" s="36" t="n"/>
     </row>
     <row r="299" ht="28" customHeight="1">
       <c r="A299" s="36" t="n"/>
@@ -22157,6 +22768,7 @@
       <c r="H299" s="39" t="n"/>
       <c r="I299" s="38" t="n"/>
       <c r="J299" s="37" t="n"/>
+      <c r="K299" s="36" t="n"/>
     </row>
     <row r="300" ht="28" customHeight="1">
       <c r="A300" s="36" t="n"/>
@@ -22169,6 +22781,7 @@
       <c r="H300" s="39" t="n"/>
       <c r="I300" s="38" t="n"/>
       <c r="J300" s="37" t="n"/>
+      <c r="K300" s="36" t="n"/>
     </row>
     <row r="301" ht="28" customHeight="1">
       <c r="A301" s="36" t="n"/>
@@ -22181,6 +22794,7 @@
       <c r="H301" s="39" t="n"/>
       <c r="I301" s="38" t="n"/>
       <c r="J301" s="37" t="n"/>
+      <c r="K301" s="36" t="n"/>
     </row>
     <row r="302" ht="28" customHeight="1">
       <c r="A302" s="36" t="n"/>
@@ -22193,6 +22807,7 @@
       <c r="H302" s="39" t="n"/>
       <c r="I302" s="38" t="n"/>
       <c r="J302" s="37" t="n"/>
+      <c r="K302" s="36" t="n"/>
     </row>
     <row r="303" ht="28" customHeight="1">
       <c r="A303" s="36" t="n"/>
@@ -22205,9 +22820,10 @@
       <c r="H303" s="39" t="n"/>
       <c r="I303" s="38" t="n"/>
       <c r="J303" s="37" t="n"/>
+      <c r="K303" s="36" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J303"/>
+  <autoFilter ref="A3:K303"/>
   <conditionalFormatting sqref="G4:G303">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="3">
       <formula>"نشط"</formula>
@@ -22216,7 +22832,7 @@
       <formula>"موقوف"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:J303">
+  <conditionalFormatting sqref="A4:K303">
     <cfRule type="expression" priority="3" dxfId="2">
       <formula>AND(MOD(ROW(),2)=1,$A4&lt;&gt;"")</formula>
     </cfRule>
